--- a/Data/04_26_schedule_results.xlsx
+++ b/Data/04_26_schedule_results.xlsx
@@ -534,11 +534,11 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,7 +554,7 @@
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3">
@@ -586,11 +586,11 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -606,7 +606,7 @@
         <v>90</v>
       </c>
       <c r="N3" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4">
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>3.5</v>
@@ -658,7 +658,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>400</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5">
@@ -690,18 +690,18 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>3.5</v>
@@ -710,7 +710,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6">
@@ -742,18 +742,18 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>3.5</v>
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7">
@@ -794,18 +794,18 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>3.5</v>
@@ -814,7 +814,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>560</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -846,18 +846,18 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>3.5</v>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>3.5</v>
@@ -918,7 +918,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10">
@@ -950,18 +950,18 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
         <v>3.5</v>
@@ -970,7 +970,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11">
@@ -1002,18 +1002,18 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>3.5</v>
@@ -1022,7 +1022,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>560</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12">
@@ -1054,18 +1054,18 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>3.5</v>
@@ -1074,7 +1074,7 @@
         <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13">
@@ -1106,18 +1106,18 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>3.5</v>
@@ -1126,7 +1126,7 @@
         <v>70</v>
       </c>
       <c r="N13" t="n">
-        <v>550</v>
+        <v>612.3</v>
       </c>
     </row>
     <row r="14">
@@ -1158,18 +1158,18 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1178,7 +1178,7 @@
         <v>70</v>
       </c>
       <c r="N14" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15">
@@ -1210,18 +1210,18 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
         <v>3.5</v>
@@ -1230,7 +1230,7 @@
         <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>390</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1282,7 +1282,7 @@
         <v>70</v>
       </c>
       <c r="N16" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17">
@@ -1314,11 +1314,11 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1334,7 +1334,7 @@
         <v>80</v>
       </c>
       <c r="N17" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18">
@@ -1377,7 +1377,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="19">
@@ -1418,18 +1418,18 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Arnar Ragn</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
         <v>8</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elísabet </t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1470,18 +1470,18 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1490,7 +1490,7 @@
         <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>612.3</v>
+        <v>610</v>
       </c>
     </row>
     <row r="21">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>70</v>
       </c>
       <c r="N21" t="n">
-        <v>400</v>
+        <v>612.3</v>
       </c>
     </row>
     <row r="22">
@@ -1574,18 +1574,18 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>400</v>
+        <v>640</v>
       </c>
     </row>
     <row r="23">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1678,18 +1678,18 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1698,7 +1698,7 @@
         <v>70</v>
       </c>
       <c r="N24" t="n">
-        <v>600</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25">
@@ -1730,18 +1730,18 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1750,7 +1750,7 @@
         <v>70</v>
       </c>
       <c r="N25" t="n">
-        <v>612.3</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1802,7 +1802,7 @@
         <v>70</v>
       </c>
       <c r="N26" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27">
@@ -1834,11 +1834,11 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1854,7 +1854,7 @@
         <v>70</v>
       </c>
       <c r="N27" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28">
@@ -1897,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -1906,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="N28" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="29">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="N29" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30">
@@ -1990,18 +1990,18 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2010,7 +2010,7 @@
         <v>70</v>
       </c>
       <c r="N30" t="n">
-        <v>410</v>
+        <v>560</v>
       </c>
     </row>
     <row r="31">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2062,7 +2062,7 @@
         <v>70</v>
       </c>
       <c r="N31" t="n">
-        <v>400</v>
+        <v>412.3</v>
       </c>
     </row>
     <row r="32">
@@ -2094,18 +2094,18 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2114,7 +2114,7 @@
         <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>410</v>
+        <v>580</v>
       </c>
     </row>
     <row r="33">
@@ -2146,18 +2146,18 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2166,7 +2166,7 @@
         <v>70</v>
       </c>
       <c r="N33" t="n">
-        <v>410</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2218,7 +2218,7 @@
         <v>70</v>
       </c>
       <c r="N34" t="n">
-        <v>612.3</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35">
@@ -2250,18 +2250,18 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         <v>70</v>
       </c>
       <c r="N35" t="n">
-        <v>580</v>
+        <v>410</v>
       </c>
     </row>
     <row r="36">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2374,7 +2374,7 @@
         <v>90</v>
       </c>
       <c r="N37" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
     </row>
     <row r="38">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J38" t="n">
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
         <v>3.5</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>650</v>
+        <v>510</v>
       </c>
     </row>
     <row r="39">
@@ -2469,7 +2469,7 @@
         <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>3.5</v>
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="40">
@@ -2521,7 +2521,7 @@
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L40" t="n">
         <v>3.5</v>
@@ -2530,7 +2530,7 @@
         <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="41">
@@ -2573,7 +2573,7 @@
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
         <v>3.5</v>
@@ -2582,7 +2582,7 @@
         <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>610</v>
+        <v>690</v>
       </c>
     </row>
     <row r="42">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J42" t="n">
         <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L42" t="n">
         <v>3.5</v>
@@ -2634,7 +2634,7 @@
         <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="43">
@@ -2666,18 +2666,18 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>3.5</v>
@@ -2686,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>630</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44">
@@ -2718,11 +2718,11 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2738,7 +2738,7 @@
         <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L45" t="n">
         <v>3.5</v>
@@ -2790,7 +2790,7 @@
         <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>580</v>
+        <v>690</v>
       </c>
     </row>
     <row r="46">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L46" t="n">
         <v>3.5</v>
@@ -2842,7 +2842,7 @@
         <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>450</v>
+        <v>540</v>
       </c>
     </row>
     <row r="47">
@@ -2874,18 +2874,18 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
         <v>3.5</v>
@@ -2894,7 +2894,7 @@
         <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>590</v>
+        <v>440</v>
       </c>
     </row>
     <row r="48">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2946,7 +2946,7 @@
         <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>540</v>
+        <v>470</v>
       </c>
     </row>
     <row r="49">
@@ -2978,18 +2978,18 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elísabet </t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
         <v>9</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elmar </t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>2</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>3.5</v>
@@ -2998,7 +2998,7 @@
         <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>462.3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="50">
@@ -3030,18 +3030,18 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
         <v>3.5</v>
@@ -3050,7 +3050,7 @@
         <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>630</v>
+        <v>740</v>
       </c>
     </row>
     <row r="51">
@@ -3093,7 +3093,7 @@
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L51" t="n">
         <v>3.5</v>
@@ -3102,7 +3102,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>680</v>
+        <v>630</v>
       </c>
     </row>
     <row r="52">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3154,7 +3154,7 @@
         <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>462.3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="53">
@@ -3186,11 +3186,11 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>420</v>
+        <v>462.3</v>
       </c>
     </row>
     <row r="54">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
         <v>3.5</v>
@@ -3258,7 +3258,7 @@
         <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>590</v>
+        <v>490</v>
       </c>
     </row>
     <row r="55">
@@ -3290,18 +3290,18 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3310,7 +3310,7 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>650</v>
+        <v>510</v>
       </c>
     </row>
     <row r="56">
@@ -3342,18 +3342,18 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3362,7 +3362,7 @@
         <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>680</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>3.5</v>
@@ -3414,7 +3414,7 @@
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>680</v>
+        <v>462.3</v>
       </c>
     </row>
     <row r="58">
@@ -3446,18 +3446,18 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J58" t="n">
         <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L58" t="n">
         <v>3.5</v>
@@ -3466,7 +3466,7 @@
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="59">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3518,7 +3518,7 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>590</v>
+        <v>640</v>
       </c>
     </row>
     <row r="60">
@@ -3561,7 +3561,7 @@
         <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L60" t="n">
         <v>4</v>
@@ -3570,7 +3570,7 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="61">
@@ -3602,18 +3602,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L61" t="n">
         <v>4</v>
@@ -3622,7 +3622,7 @@
         <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>710</v>
+        <v>462.3</v>
       </c>
     </row>
     <row r="62">
@@ -3706,11 +3706,11 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3726,7 +3726,7 @@
         <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="64">
@@ -3758,18 +3758,18 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -3778,7 +3778,7 @@
         <v>50</v>
       </c>
       <c r="N64" t="n">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="65">
@@ -3810,18 +3810,18 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L65" t="n">
         <v>4</v>
@@ -3830,7 +3830,7 @@
         <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>490</v>
+        <v>720</v>
       </c>
     </row>
     <row r="66">
@@ -3873,7 +3873,7 @@
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L66" t="n">
         <v>4</v>
@@ -3882,7 +3882,7 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>700</v>
+        <v>670</v>
       </c>
     </row>
     <row r="67">
@@ -3914,18 +3914,18 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J67" t="n">
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -3934,7 +3934,7 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>462.3</v>
+        <v>700</v>
       </c>
     </row>
     <row r="68">
@@ -3977,7 +3977,7 @@
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -4018,18 +4018,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J69" t="n">
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -4038,7 +4038,7 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="70">
@@ -4070,18 +4070,18 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J70" t="n">
         <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L70" t="n">
         <v>4</v>
@@ -4090,7 +4090,7 @@
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="71">
@@ -4133,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4142,7 +4142,7 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>710</v>
+        <v>580</v>
       </c>
     </row>
     <row r="72">
@@ -4174,18 +4174,18 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J72" t="n">
         <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>5</v>
@@ -4194,7 +4194,7 @@
         <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>520</v>
+        <v>470</v>
       </c>
     </row>
     <row r="73">
@@ -4226,18 +4226,18 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J73" t="n">
         <v>2</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>5</v>
@@ -4246,7 +4246,7 @@
         <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>430</v>
+        <v>522.3</v>
       </c>
     </row>
     <row r="74">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4298,7 +4298,7 @@
         <v>40</v>
       </c>
       <c r="N74" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="75">
@@ -4330,11 +4330,11 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4350,7 +4350,7 @@
         <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>570</v>
+        <v>530</v>
       </c>
     </row>
     <row r="76">
@@ -4382,11 +4382,11 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4434,11 +4434,11 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4454,7 +4454,7 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="78">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4506,7 +4506,7 @@
         <v>80</v>
       </c>
       <c r="N78" t="n">
-        <v>530</v>
+        <v>570</v>
       </c>
     </row>
     <row r="79">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4558,7 +4558,7 @@
         <v>80</v>
       </c>
       <c r="N79" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="80">
@@ -4590,11 +4590,11 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="81">
@@ -4642,18 +4642,18 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J81" t="n">
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4694,18 +4694,18 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>650</v>
+        <v>540</v>
       </c>
     </row>
     <row r="83">
@@ -4746,11 +4746,11 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>460</v>
+        <v>490</v>
       </c>
     </row>
     <row r="84">
@@ -4798,18 +4798,18 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J84" t="n">
         <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -4818,7 +4818,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>470</v>
+        <v>660</v>
       </c>
     </row>
     <row r="85">
@@ -4850,18 +4850,18 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>662.3</v>
+        <v>670</v>
       </c>
     </row>
     <row r="86">
@@ -4902,18 +4902,18 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>630</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87">
@@ -4954,18 +4954,18 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -4974,7 +4974,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="88">
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>650</v>
+        <v>662.3</v>
       </c>
     </row>
     <row r="89">
@@ -5058,15 +5058,15 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" t="n">
         <v>9</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>660</v>
+        <v>610</v>
       </c>
     </row>
     <row r="90">
@@ -5110,11 +5110,11 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>540</v>
+        <v>450</v>
       </c>
     </row>
     <row r="91">
@@ -5162,18 +5162,18 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J91" t="n">
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L91" t="n">
         <v>5</v>
@@ -5182,7 +5182,7 @@
         <v>70</v>
       </c>
       <c r="N91" t="n">
-        <v>410</v>
+        <v>672.3</v>
       </c>
     </row>
     <row r="92">
@@ -5214,18 +5214,18 @@
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J92" t="n">
         <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>5</v>
@@ -5234,7 +5234,7 @@
         <v>70</v>
       </c>
       <c r="N92" t="n">
-        <v>610</v>
+        <v>412.3</v>
       </c>
     </row>
     <row r="93">
@@ -5266,18 +5266,18 @@
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J93" t="n">
         <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
         <v>5</v>
@@ -5286,7 +5286,7 @@
         <v>70</v>
       </c>
       <c r="N93" t="n">
-        <v>412.3</v>
+        <v>420</v>
       </c>
     </row>
     <row r="94">
@@ -5318,18 +5318,18 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J94" t="n">
         <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
         <v>5</v>
@@ -5338,7 +5338,7 @@
         <v>70</v>
       </c>
       <c r="N94" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95">
@@ -5370,18 +5370,18 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J95" t="n">
         <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L95" t="n">
         <v>5</v>
@@ -5390,7 +5390,7 @@
         <v>70</v>
       </c>
       <c r="N95" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="96">
@@ -5474,18 +5474,18 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L97" t="n">
         <v>5.5</v>
@@ -5494,7 +5494,7 @@
         <v>70</v>
       </c>
       <c r="N97" t="n">
-        <v>570</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98">
@@ -5526,11 +5526,11 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5546,7 +5546,7 @@
         <v>70</v>
       </c>
       <c r="N98" t="n">
-        <v>710</v>
+        <v>610</v>
       </c>
     </row>
     <row r="99">
@@ -5578,18 +5578,18 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J99" t="n">
         <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L99" t="n">
         <v>5.5</v>
@@ -5598,7 +5598,7 @@
         <v>70</v>
       </c>
       <c r="N99" t="n">
-        <v>690</v>
+        <v>412.3</v>
       </c>
     </row>
     <row r="100">
@@ -5630,18 +5630,18 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J100" t="n">
         <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L100" t="n">
         <v>5.5</v>
@@ -5682,18 +5682,18 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J101" t="n">
         <v>2</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L101" t="n">
         <v>5.5</v>
@@ -5702,7 +5702,7 @@
         <v>70</v>
       </c>
       <c r="N101" t="n">
-        <v>412.3</v>
+        <v>440</v>
       </c>
     </row>
     <row r="102">
@@ -5734,11 +5734,11 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5754,7 +5754,7 @@
         <v>70</v>
       </c>
       <c r="N102" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="103">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L103" t="n">
         <v>5.5</v>
@@ -5806,7 +5806,7 @@
         <v>70</v>
       </c>
       <c r="N103" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
     </row>
     <row r="104">
@@ -5838,18 +5838,18 @@
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J104" t="n">
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L104" t="n">
         <v>5.5</v>
@@ -5858,7 +5858,7 @@
         <v>70</v>
       </c>
       <c r="N104" t="n">
-        <v>412.3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="105">
@@ -5890,18 +5890,18 @@
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J105" t="n">
         <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
         <v>5.5</v>
@@ -5910,7 +5910,7 @@
         <v>70</v>
       </c>
       <c r="N105" t="n">
-        <v>420</v>
+        <v>390</v>
       </c>
     </row>
     <row r="106">
@@ -5942,11 +5942,11 @@
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5962,7 +5962,7 @@
         <v>70</v>
       </c>
       <c r="N106" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="107">
@@ -6005,7 +6005,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L107" t="n">
         <v>4</v>
@@ -6014,7 +6014,7 @@
         <v>70</v>
       </c>
       <c r="N107" t="n">
-        <v>570</v>
+        <v>410</v>
       </c>
     </row>
     <row r="108">
@@ -6046,18 +6046,18 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J108" t="n">
         <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L108" t="n">
         <v>4</v>
@@ -6066,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="N108" t="n">
-        <v>440</v>
+        <v>730</v>
       </c>
     </row>
     <row r="109">
@@ -6098,18 +6098,18 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J109" t="n">
         <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L109" t="n">
         <v>4</v>
@@ -6118,7 +6118,7 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>440</v>
+        <v>682.3</v>
       </c>
     </row>
     <row r="110">
@@ -6150,18 +6150,18 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J110" t="n">
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L110" t="n">
         <v>4</v>
@@ -6170,7 +6170,7 @@
         <v>70</v>
       </c>
       <c r="N110" t="n">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="111">
@@ -6202,18 +6202,18 @@
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>4</v>
@@ -6254,18 +6254,18 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L112" t="n">
         <v>4</v>
@@ -6274,7 +6274,7 @@
         <v>70</v>
       </c>
       <c r="N112" t="n">
-        <v>682.3</v>
+        <v>440</v>
       </c>
     </row>
     <row r="113">
@@ -6306,18 +6306,18 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J113" t="n">
         <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L113" t="n">
         <v>4</v>
@@ -6326,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="N113" t="n">
-        <v>690</v>
+        <v>410</v>
       </c>
     </row>
     <row r="114">
@@ -6358,18 +6358,18 @@
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J114" t="n">
         <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L114" t="n">
         <v>4</v>
@@ -6378,7 +6378,7 @@
         <v>70</v>
       </c>
       <c r="N114" t="n">
-        <v>590</v>
+        <v>690</v>
       </c>
     </row>
     <row r="115">
@@ -6410,11 +6410,11 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6430,7 +6430,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="116">
@@ -6473,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L116" t="n">
         <v>4</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>510</v>
+        <v>760</v>
       </c>
     </row>
     <row r="117">
@@ -6525,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>4</v>
@@ -6534,7 +6534,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>660</v>
+        <v>420</v>
       </c>
     </row>
     <row r="118">
@@ -6618,11 +6618,11 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6638,7 +6638,7 @@
         <v>80</v>
       </c>
       <c r="N119" t="n">
-        <v>530</v>
+        <v>550</v>
       </c>
     </row>
     <row r="120">
@@ -6670,11 +6670,11 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="N120" t="n">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="121">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6742,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>540</v>
+        <v>570</v>
       </c>
     </row>
     <row r="122">
@@ -6774,11 +6774,11 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6794,7 +6794,7 @@
         <v>40</v>
       </c>
       <c r="N122" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
     </row>
     <row r="123">
@@ -6826,11 +6826,11 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6846,7 +6846,7 @@
         <v>90</v>
       </c>
       <c r="N123" t="n">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="124">
@@ -6878,18 +6878,18 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J124" t="n">
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
@@ -6898,7 +6898,7 @@
         <v>80</v>
       </c>
       <c r="N124" t="n">
-        <v>492.3</v>
+        <v>542.3</v>
       </c>
     </row>
     <row r="125">
@@ -6930,11 +6930,11 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -6950,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="N125" t="n">
-        <v>570</v>
+        <v>620</v>
       </c>
     </row>
     <row r="126">
@@ -6982,18 +6982,18 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J126" t="n">
         <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L126" t="n">
         <v>3</v>
@@ -7002,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="N126" t="n">
-        <v>542.3</v>
+        <v>602.3</v>
       </c>
     </row>
     <row r="127">
@@ -7034,18 +7034,18 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7054,7 +7054,7 @@
         <v>80</v>
       </c>
       <c r="N127" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128">
@@ -7086,18 +7086,18 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L128" t="n">
         <v>3</v>
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>650</v>
+        <v>560</v>
       </c>
     </row>
     <row r="129">
@@ -7138,18 +7138,18 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L129" t="n">
         <v>3</v>
@@ -7158,7 +7158,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>450</v>
+        <v>640</v>
       </c>
     </row>
     <row r="130">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>690</v>
+        <v>590</v>
       </c>
     </row>
     <row r="131">
@@ -7242,18 +7242,18 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J131" t="n">
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
         <v>3</v>
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>630</v>
+        <v>392.3</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L132" t="n">
         <v>3</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="133">
@@ -7398,11 +7398,11 @@
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7418,7 +7418,7 @@
         <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
     </row>
     <row r="135">
@@ -7450,18 +7450,18 @@
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J135" t="n">
         <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
         <v>4</v>
@@ -7470,7 +7470,7 @@
         <v>80</v>
       </c>
       <c r="N135" t="n">
-        <v>530</v>
+        <v>410</v>
       </c>
     </row>
     <row r="136">
@@ -7502,18 +7502,18 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J136" t="n">
         <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="n">
         <v>4</v>
@@ -7522,7 +7522,7 @@
         <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>400</v>
+        <v>530</v>
       </c>
     </row>
     <row r="137">
@@ -7554,11 +7554,11 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7574,7 +7574,7 @@
         <v>100</v>
       </c>
       <c r="N137" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="138">
@@ -7606,11 +7606,11 @@
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -7658,11 +7658,11 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7678,7 +7678,7 @@
         <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>542.3</v>
+        <v>550</v>
       </c>
     </row>
     <row r="140">
@@ -7710,18 +7710,18 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J140" t="n">
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -7730,7 +7730,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
     </row>
     <row r="141">
@@ -7762,18 +7762,18 @@
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J141" t="n">
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row r="142">
@@ -7814,18 +7814,18 @@
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row r="143">
@@ -7866,18 +7866,18 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J143" t="n">
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -7886,7 +7886,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144">
@@ -7918,18 +7918,18 @@
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J144" t="n">
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L144" t="n">
         <v>4</v>
@@ -7938,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="N144" t="n">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row r="145">
@@ -7970,18 +7970,18 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J145" t="n">
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>580</v>
+        <v>530</v>
       </c>
     </row>
     <row r="146">
@@ -8022,18 +8022,18 @@
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8042,7 +8042,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="147">
@@ -8074,18 +8074,18 @@
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J147" t="n">
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8094,7 +8094,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="148">
@@ -8126,18 +8126,18 @@
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J148" t="n">
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8146,7 +8146,7 @@
         <v>50</v>
       </c>
       <c r="N148" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
     </row>
     <row r="149">
@@ -8189,7 +8189,7 @@
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8198,7 +8198,7 @@
         <v>50</v>
       </c>
       <c r="N149" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
     </row>
     <row r="150">
@@ -8241,7 +8241,7 @@
         <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L150" t="n">
         <v>4</v>
@@ -8250,7 +8250,7 @@
         <v>50</v>
       </c>
       <c r="N150" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
     </row>
     <row r="151">
@@ -8334,18 +8334,18 @@
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J152" t="n">
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L152" t="n">
         <v>4</v>
@@ -8354,7 +8354,7 @@
         <v>70</v>
       </c>
       <c r="N152" t="n">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153">
@@ -8397,7 +8397,7 @@
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L153" t="n">
         <v>4</v>
@@ -8406,7 +8406,7 @@
         <v>70</v>
       </c>
       <c r="N153" t="n">
-        <v>440</v>
+        <v>590</v>
       </c>
     </row>
     <row r="154">
@@ -8438,18 +8438,18 @@
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J154" t="n">
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L154" t="n">
         <v>4</v>
@@ -8458,7 +8458,7 @@
         <v>70</v>
       </c>
       <c r="N154" t="n">
-        <v>640</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155">
@@ -8501,7 +8501,7 @@
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L155" t="n">
         <v>4</v>
@@ -8510,7 +8510,7 @@
         <v>70</v>
       </c>
       <c r="N155" t="n">
-        <v>412.3</v>
+        <v>462.3</v>
       </c>
     </row>
     <row r="156">
@@ -8542,11 +8542,11 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8562,7 +8562,7 @@
         <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157">
@@ -8594,18 +8594,18 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J157" t="n">
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L157" t="n">
         <v>4</v>
@@ -8614,7 +8614,7 @@
         <v>70</v>
       </c>
       <c r="N157" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="158">
@@ -8646,11 +8646,11 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8666,7 +8666,7 @@
         <v>70</v>
       </c>
       <c r="N158" t="n">
-        <v>490</v>
+        <v>590</v>
       </c>
     </row>
     <row r="159">
@@ -8709,7 +8709,7 @@
         <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L159" t="n">
         <v>4</v>
@@ -8718,7 +8718,7 @@
         <v>70</v>
       </c>
       <c r="N159" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="160">
@@ -8750,18 +8750,18 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J160" t="n">
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
@@ -8770,7 +8770,7 @@
         <v>80</v>
       </c>
       <c r="N160" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="161">
@@ -8802,18 +8802,18 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J161" t="n">
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>3</v>
@@ -8822,7 +8822,7 @@
         <v>80</v>
       </c>
       <c r="N161" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="162">
@@ -8854,11 +8854,11 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -8874,7 +8874,7 @@
         <v>90</v>
       </c>
       <c r="N162" t="n">
-        <v>530</v>
+        <v>490</v>
       </c>
     </row>
     <row r="163">
@@ -8906,18 +8906,18 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J163" t="n">
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -8926,7 +8926,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>660</v>
+        <v>420</v>
       </c>
     </row>
     <row r="164">
@@ -8958,18 +8958,18 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>662.3</v>
+        <v>670</v>
       </c>
     </row>
     <row r="165">
@@ -9010,18 +9010,18 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
+        <v>15</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Hrafnkell</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>2</v>
+      </c>
+      <c r="K165" t="n">
         <v>10</v>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Erna </t>
-        </is>
-      </c>
-      <c r="J165" t="n">
-        <v>2</v>
-      </c>
-      <c r="K165" t="n">
-        <v>1</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>490</v>
+        <v>670</v>
       </c>
     </row>
     <row r="166">
@@ -9062,18 +9062,18 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9082,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>650</v>
+        <v>710</v>
       </c>
     </row>
     <row r="167">
@@ -9114,18 +9114,18 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J167" t="n">
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9134,7 +9134,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
     </row>
     <row r="168">
@@ -9166,18 +9166,18 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9186,7 +9186,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>490</v>
+        <v>650</v>
       </c>
     </row>
     <row r="169">
@@ -9218,18 +9218,18 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9238,7 +9238,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row r="170">
@@ -9270,18 +9270,18 @@
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J170" t="n">
         <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L170" t="n">
         <v>3</v>
@@ -9290,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>640</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171">
@@ -9322,18 +9322,18 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K171" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L171" t="n">
         <v>3</v>
@@ -9342,7 +9342,7 @@
         <v>50</v>
       </c>
       <c r="N171" t="n">
-        <v>650</v>
+        <v>690</v>
       </c>
     </row>
     <row r="172">
@@ -9374,18 +9374,18 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
@@ -9394,7 +9394,7 @@
         <v>50</v>
       </c>
       <c r="N172" t="n">
-        <v>600</v>
+        <v>570</v>
       </c>
     </row>
     <row r="173">
@@ -9426,11 +9426,11 @@
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9446,7 +9446,7 @@
         <v>50</v>
       </c>
       <c r="N173" t="n">
-        <v>560</v>
+        <v>530</v>
       </c>
     </row>
     <row r="174">
@@ -9478,18 +9478,18 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J174" t="n">
         <v>2</v>
       </c>
       <c r="K174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
         <v>3</v>
@@ -9498,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>530</v>
+        <v>570</v>
       </c>
     </row>
     <row r="175">
@@ -9530,18 +9530,18 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J175" t="n">
         <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
@@ -9771,19 +9771,19 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
         <v>1</v>
@@ -9792,10 +9792,10 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -9818,9 +9818,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>1</v>
@@ -9831,23 +9829,23 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -9856,7 +9854,9 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -9872,27 +9872,27 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9928,10 +9928,10 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -10011,14 +10011,14 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -10026,32 +10026,32 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -10069,35 +10069,35 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10106,7 +10106,9 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -10116,7 +10118,9 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -10125,18 +10129,16 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
@@ -10148,9 +10150,7 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -10173,19 +10173,19 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
       <c r="AA12" t="n">
         <v>1</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10203,7 +10203,9 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>1</v>
@@ -10211,9 +10213,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -10241,45 +10241,45 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10304,36 +10304,38 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -10345,22 +10347,20 @@
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -10380,19 +10380,19 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
@@ -10402,10 +10402,10 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -10417,7 +10417,9 @@
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -10426,30 +10428,30 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
@@ -10500,8 +10502,12 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -10512,42 +10518,38 @@
         <v>1</v>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -10559,10 +10561,10 @@
       <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -10577,14 +10579,16 @@
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10628,20 +10632,20 @@
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -10656,17 +10660,17 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10686,27 +10690,27 @@
       <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -10717,9 +10721,7 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
@@ -10728,7 +10730,9 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -10744,9 +10748,7 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
         <v>1</v>
@@ -10795,18 +10797,20 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
@@ -10814,22 +10818,22 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -10848,20 +10852,20 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
@@ -10869,10 +10873,10 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
@@ -10901,10 +10905,10 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
@@ -10926,9 +10930,7 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -10945,7 +10947,9 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>1</v>
@@ -10956,10 +10960,10 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
@@ -10969,19 +10973,21 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>1</v>
@@ -10989,10 +10995,10 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -11008,46 +11014,42 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
@@ -11057,16 +11059,18 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -11074,10 +11078,10 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -11085,19 +11089,19 @@
       <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
@@ -11108,7 +11112,9 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -11126,10 +11132,10 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
         <v>1</v>
       </c>
@@ -11137,17 +11143,15 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11188,23 +11192,21 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -11212,12 +11214,16 @@
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
@@ -11226,9 +11232,7 @@
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -11236,32 +11240,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
@@ -11282,9 +11284,7 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>1</v>
       </c>
@@ -11294,45 +11294,45 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -11340,17 +11340,17 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
@@ -11362,7 +11362,9 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
@@ -11388,18 +11390,16 @@
         <v>1</v>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
         <v>1</v>
       </c>
@@ -11407,15 +11407,17 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
       <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -11436,7 +11438,9 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
@@ -11448,9 +11452,7 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
         <v>1</v>
       </c>
@@ -11464,34 +11466,30 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>1</v>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -11505,7 +11503,9 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/04_26_schedule_results.xlsx
+++ b/Data/04_26_schedule_results.xlsx
@@ -586,15 +586,15 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4">
@@ -638,11 +638,11 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -658,7 +658,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>520</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5">
@@ -690,18 +690,18 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>3.5</v>
@@ -710,7 +710,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>610</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -742,18 +742,18 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>3.5</v>
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>612.3</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7">
@@ -794,18 +794,18 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>3.5</v>
@@ -814,7 +814,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>400</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -846,18 +846,18 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>3.5</v>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>400</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9">
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>3.5</v>
@@ -950,18 +950,18 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>3.5</v>
@@ -970,7 +970,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="11">
@@ -1002,18 +1002,18 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>3.5</v>
@@ -1022,7 +1022,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>640</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12">
@@ -1054,18 +1054,18 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>3.5</v>
@@ -1074,7 +1074,7 @@
         <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>610</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13">
@@ -1106,18 +1106,18 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
         <v>3.5</v>
@@ -1126,7 +1126,7 @@
         <v>70</v>
       </c>
       <c r="N13" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14">
@@ -1158,18 +1158,18 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1178,7 +1178,7 @@
         <v>70</v>
       </c>
       <c r="N14" t="n">
-        <v>390</v>
+        <v>652.3</v>
       </c>
     </row>
     <row r="15">
@@ -1334,7 +1334,7 @@
         <v>80</v>
       </c>
       <c r="N17" t="n">
-        <v>560</v>
+        <v>610</v>
       </c>
     </row>
     <row r="18">
@@ -1377,7 +1377,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
@@ -1429,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>70</v>
       </c>
       <c r="N21" t="n">
-        <v>610</v>
+        <v>612.3</v>
       </c>
     </row>
     <row r="22">
@@ -1574,18 +1574,18 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>600</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23">
@@ -1626,18 +1626,18 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>410</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24">
@@ -1741,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1793,7 +1793,7 @@
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1897,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -1906,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="N28" t="n">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29">
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="N29" t="n">
-        <v>490</v>
+        <v>590</v>
       </c>
     </row>
     <row r="30">
@@ -2010,7 +2010,7 @@
         <v>70</v>
       </c>
       <c r="N30" t="n">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="31">
@@ -2114,7 +2114,7 @@
         <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2374,7 +2374,7 @@
         <v>90</v>
       </c>
       <c r="N37" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J38" t="n">
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>3.5</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>510</v>
+        <v>460</v>
       </c>
     </row>
     <row r="39">
@@ -2458,18 +2458,18 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J39" t="n">
         <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L39" t="n">
         <v>3.5</v>
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="40">
@@ -2510,18 +2510,18 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J40" t="n">
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
         <v>3.5</v>
@@ -2573,7 +2573,7 @@
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
         <v>3.5</v>
@@ -2582,7 +2582,7 @@
         <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
     </row>
     <row r="42">
@@ -2634,7 +2634,7 @@
         <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="43">
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
         <v>3.5</v>
@@ -2686,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="44">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>3.5</v>
@@ -2738,7 +2738,7 @@
         <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>460</v>
+        <v>490</v>
       </c>
     </row>
     <row r="45">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L45" t="n">
         <v>3.5</v>
@@ -2790,7 +2790,7 @@
         <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
     </row>
     <row r="46">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L46" t="n">
         <v>3.5</v>
@@ -2842,7 +2842,7 @@
         <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>460</v>
+        <v>650</v>
       </c>
     </row>
     <row r="47">
@@ -2874,11 +2874,11 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2894,7 +2894,7 @@
         <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="48">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2946,7 +2946,7 @@
         <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49">
@@ -2978,18 +2978,18 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J49" t="n">
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L49" t="n">
         <v>3.5</v>
@@ -2998,7 +2998,7 @@
         <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>710</v>
+        <v>650</v>
       </c>
     </row>
     <row r="50">
@@ -3030,18 +3030,18 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L50" t="n">
         <v>3.5</v>
@@ -3050,7 +3050,7 @@
         <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>630</v>
+        <v>462.3</v>
       </c>
     </row>
     <row r="51">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L51" t="n">
         <v>3.5</v>
@@ -3102,7 +3102,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>462.3</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3154,7 +3154,7 @@
         <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
     </row>
     <row r="53">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>3.5</v>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>530</v>
+        <v>490</v>
       </c>
     </row>
     <row r="54">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L54" t="n">
         <v>3.5</v>
@@ -3258,7 +3258,7 @@
         <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>700</v>
+        <v>702.3</v>
       </c>
     </row>
     <row r="55">
@@ -3290,18 +3290,18 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3310,7 +3310,7 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>462.3</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56">
@@ -3342,18 +3342,18 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3362,7 +3362,7 @@
         <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>470</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L57" t="n">
         <v>3.5</v>
@@ -3414,7 +3414,7 @@
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58">
@@ -3446,18 +3446,18 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>3.5</v>
@@ -3466,7 +3466,7 @@
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="59">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3518,7 +3518,7 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>610</v>
+        <v>640</v>
       </c>
     </row>
     <row r="60">
@@ -3550,11 +3550,11 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3570,7 +3570,7 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61">
@@ -3706,18 +3706,18 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -3726,7 +3726,7 @@
         <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>462.3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="64">
@@ -3758,18 +3758,18 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -3810,18 +3810,18 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L65" t="n">
         <v>4</v>
@@ -3862,18 +3862,18 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
         <v>4</v>
@@ -3882,7 +3882,7 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>710</v>
+        <v>690</v>
       </c>
     </row>
     <row r="67">
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -3934,7 +3934,7 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>490</v>
+        <v>710</v>
       </c>
     </row>
     <row r="68">
@@ -3966,18 +3966,18 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -3986,7 +3986,7 @@
         <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>692.3</v>
+        <v>490</v>
       </c>
     </row>
     <row r="69">
@@ -4018,18 +4018,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J69" t="n">
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -4038,7 +4038,7 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>700</v>
+        <v>460</v>
       </c>
     </row>
     <row r="70">
@@ -4070,11 +4070,11 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4122,11 +4122,11 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4142,7 +4142,7 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>590</v>
+        <v>690</v>
       </c>
     </row>
     <row r="72">
@@ -4174,18 +4174,18 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J72" t="n">
         <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>5</v>
@@ -4194,7 +4194,7 @@
         <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>522.3</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73">
@@ -4226,18 +4226,18 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J73" t="n">
         <v>2</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>5</v>
@@ -4246,7 +4246,7 @@
         <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4298,7 +4298,7 @@
         <v>40</v>
       </c>
       <c r="N74" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="75">
@@ -4330,11 +4330,11 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4350,7 +4350,7 @@
         <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>570</v>
+        <v>572.3</v>
       </c>
     </row>
     <row r="76">
@@ -4382,11 +4382,11 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4402,7 +4402,7 @@
         <v>40</v>
       </c>
       <c r="N76" t="n">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="77">
@@ -4434,11 +4434,11 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4454,7 +4454,7 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>540</v>
+        <v>502.3</v>
       </c>
     </row>
     <row r="78">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4590,18 +4590,18 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="81">
@@ -4642,18 +4642,18 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J81" t="n">
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4662,7 +4662,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>660</v>
+        <v>662.3</v>
       </c>
     </row>
     <row r="82">
@@ -4694,18 +4694,18 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>450</v>
+        <v>710</v>
       </c>
     </row>
     <row r="83">
@@ -4746,18 +4746,18 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>660</v>
+        <v>500</v>
       </c>
     </row>
     <row r="84">
@@ -4798,18 +4798,18 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J84" t="n">
         <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -4818,7 +4818,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>690</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85">
@@ -4850,18 +4850,18 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
     </row>
     <row r="86">
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>660</v>
+        <v>710</v>
       </c>
     </row>
     <row r="87">
@@ -4954,18 +4954,18 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -4974,7 +4974,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>480</v>
+        <v>650</v>
       </c>
     </row>
     <row r="88">
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="89">
@@ -5058,18 +5058,18 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J89" t="n">
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>640</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90">
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>540</v>
+        <v>570</v>
       </c>
     </row>
     <row r="91">
@@ -5338,7 +5338,7 @@
         <v>70</v>
       </c>
       <c r="N94" t="n">
-        <v>672.3</v>
+        <v>642.3</v>
       </c>
     </row>
     <row r="95">
@@ -5474,18 +5474,18 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L97" t="n">
         <v>5.5</v>
@@ -5494,7 +5494,7 @@
         <v>70</v>
       </c>
       <c r="N97" t="n">
-        <v>400</v>
+        <v>580</v>
       </c>
     </row>
     <row r="98">
@@ -5526,18 +5526,18 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
         <v>5.5</v>
@@ -5546,7 +5546,7 @@
         <v>70</v>
       </c>
       <c r="N98" t="n">
-        <v>570</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99">
@@ -5630,18 +5630,18 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J100" t="n">
         <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L100" t="n">
         <v>5.5</v>
@@ -5650,7 +5650,7 @@
         <v>70</v>
       </c>
       <c r="N100" t="n">
-        <v>630</v>
+        <v>610</v>
       </c>
     </row>
     <row r="101">
@@ -5745,7 +5745,7 @@
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L102" t="n">
         <v>5.5</v>
@@ -5754,7 +5754,7 @@
         <v>70</v>
       </c>
       <c r="N102" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
     </row>
     <row r="103">
@@ -5797,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L103" t="n">
         <v>5.5</v>
@@ -5806,7 +5806,7 @@
         <v>70</v>
       </c>
       <c r="N103" t="n">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="104">
@@ -5849,7 +5849,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L104" t="n">
         <v>5.5</v>
@@ -5858,7 +5858,7 @@
         <v>70</v>
       </c>
       <c r="N104" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
     </row>
     <row r="105">
@@ -5962,7 +5962,7 @@
         <v>70</v>
       </c>
       <c r="N106" t="n">
-        <v>420</v>
+        <v>470</v>
       </c>
     </row>
     <row r="107">
@@ -6046,11 +6046,11 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6066,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="N108" t="n">
-        <v>682.3</v>
+        <v>560</v>
       </c>
     </row>
     <row r="109">
@@ -6098,11 +6098,11 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6118,7 +6118,7 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="110">
@@ -6150,18 +6150,18 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J110" t="n">
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L110" t="n">
         <v>4</v>
@@ -6170,7 +6170,7 @@
         <v>70</v>
       </c>
       <c r="N110" t="n">
-        <v>440</v>
+        <v>590</v>
       </c>
     </row>
     <row r="111">
@@ -6202,18 +6202,18 @@
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L111" t="n">
         <v>4</v>
@@ -6222,7 +6222,7 @@
         <v>70</v>
       </c>
       <c r="N111" t="n">
-        <v>710</v>
+        <v>440</v>
       </c>
     </row>
     <row r="112">
@@ -6254,18 +6254,18 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L112" t="n">
         <v>4</v>
@@ -6274,7 +6274,7 @@
         <v>70</v>
       </c>
       <c r="N112" t="n">
-        <v>440</v>
+        <v>712.3</v>
       </c>
     </row>
     <row r="113">
@@ -6306,18 +6306,18 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J113" t="n">
         <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L113" t="n">
         <v>4</v>
@@ -6326,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="N113" t="n">
-        <v>410</v>
+        <v>440</v>
       </c>
     </row>
     <row r="114">
@@ -6358,18 +6358,18 @@
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J114" t="n">
         <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L114" t="n">
         <v>4</v>
@@ -6378,7 +6378,7 @@
         <v>70</v>
       </c>
       <c r="N114" t="n">
-        <v>710</v>
+        <v>410</v>
       </c>
     </row>
     <row r="115">
@@ -6410,18 +6410,18 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L115" t="n">
         <v>4</v>
@@ -6430,7 +6430,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>510</v>
+        <v>610</v>
       </c>
     </row>
     <row r="116">
@@ -6462,18 +6462,18 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J116" t="n">
         <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>4</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="117">
@@ -6514,18 +6514,18 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J117" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L117" t="n">
         <v>4</v>
@@ -6534,7 +6534,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>470</v>
+        <v>640</v>
       </c>
     </row>
     <row r="118">
@@ -6566,18 +6566,18 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J118" t="n">
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L118" t="n">
         <v>4</v>
@@ -6586,7 +6586,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>710</v>
+        <v>540</v>
       </c>
     </row>
     <row r="119">
@@ -6618,11 +6618,11 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6638,7 +6638,7 @@
         <v>80</v>
       </c>
       <c r="N119" t="n">
-        <v>542.3</v>
+        <v>560</v>
       </c>
     </row>
     <row r="120">
@@ -6670,11 +6670,11 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="N120" t="n">
-        <v>550</v>
+        <v>580</v>
       </c>
     </row>
     <row r="121">
@@ -6774,11 +6774,11 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6794,7 +6794,7 @@
         <v>40</v>
       </c>
       <c r="N122" t="n">
-        <v>480</v>
+        <v>430</v>
       </c>
     </row>
     <row r="123">
@@ -6826,15 +6826,15 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>90</v>
       </c>
       <c r="N123" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="124">
@@ -6878,18 +6878,18 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J124" t="n">
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
@@ -6898,7 +6898,7 @@
         <v>80</v>
       </c>
       <c r="N124" t="n">
-        <v>542.3</v>
+        <v>530</v>
       </c>
     </row>
     <row r="125">
@@ -6930,11 +6930,11 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -6950,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="N125" t="n">
-        <v>602.3</v>
+        <v>580</v>
       </c>
     </row>
     <row r="126">
@@ -6982,11 +6982,11 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7002,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="N126" t="n">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="127">
@@ -7034,18 +7034,18 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7086,18 +7086,18 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L128" t="n">
         <v>3</v>
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129">
@@ -7138,18 +7138,18 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L129" t="n">
         <v>3</v>
@@ -7158,7 +7158,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
     </row>
     <row r="130">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>580</v>
+        <v>392.3</v>
       </c>
     </row>
     <row r="131">
@@ -7242,18 +7242,18 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J131" t="n">
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L131" t="n">
         <v>3</v>
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>392.3</v>
+        <v>470</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L132" t="n">
         <v>3</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>490</v>
+        <v>700</v>
       </c>
     </row>
     <row r="133">
@@ -7346,18 +7346,18 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J133" t="n">
         <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7366,7 +7366,7 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>460</v>
+        <v>730</v>
       </c>
     </row>
     <row r="134">
@@ -7398,11 +7398,11 @@
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7418,7 +7418,7 @@
         <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>590</v>
+        <v>470</v>
       </c>
     </row>
     <row r="135">
@@ -7502,11 +7502,11 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7522,7 +7522,7 @@
         <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>540</v>
+        <v>492.3</v>
       </c>
     </row>
     <row r="137">
@@ -7554,11 +7554,11 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7574,7 +7574,7 @@
         <v>100</v>
       </c>
       <c r="N137" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="138">
@@ -7606,18 +7606,18 @@
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J138" t="n">
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" t="n">
         <v>4</v>
@@ -7626,7 +7626,7 @@
         <v>80</v>
       </c>
       <c r="N138" t="n">
-        <v>570</v>
+        <v>542.3</v>
       </c>
     </row>
     <row r="139">
@@ -7658,18 +7658,18 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J139" t="n">
         <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>4</v>
@@ -7678,7 +7678,7 @@
         <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>570</v>
+        <v>582.3</v>
       </c>
     </row>
     <row r="140">
@@ -7762,18 +7762,18 @@
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J141" t="n">
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>610</v>
+        <v>470</v>
       </c>
     </row>
     <row r="142">
@@ -7970,18 +7970,18 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J145" t="n">
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="146">
@@ -8022,18 +8022,18 @@
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8042,7 +8042,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>590</v>
+        <v>540</v>
       </c>
     </row>
     <row r="147">
@@ -8074,18 +8074,18 @@
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J147" t="n">
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8094,7 +8094,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>592.3</v>
+        <v>540</v>
       </c>
     </row>
     <row r="148">
@@ -8126,18 +8126,18 @@
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J148" t="n">
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8146,7 +8146,7 @@
         <v>50</v>
       </c>
       <c r="N148" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
     </row>
     <row r="149">
@@ -8282,11 +8282,11 @@
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -8386,18 +8386,18 @@
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J153" t="n">
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L153" t="n">
         <v>4</v>
@@ -8406,7 +8406,7 @@
         <v>70</v>
       </c>
       <c r="N153" t="n">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154">
@@ -8438,18 +8438,18 @@
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J154" t="n">
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L154" t="n">
         <v>4</v>
@@ -8458,7 +8458,7 @@
         <v>70</v>
       </c>
       <c r="N154" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155">
@@ -8490,18 +8490,18 @@
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J155" t="n">
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L155" t="n">
         <v>4</v>
@@ -8510,7 +8510,7 @@
         <v>70</v>
       </c>
       <c r="N155" t="n">
-        <v>462.3</v>
+        <v>560</v>
       </c>
     </row>
     <row r="156">
@@ -8542,18 +8542,18 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J156" t="n">
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L156" t="n">
         <v>4</v>
@@ -8562,7 +8562,7 @@
         <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>420</v>
+        <v>530</v>
       </c>
     </row>
     <row r="157">
@@ -8646,18 +8646,18 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K158" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L158" t="n">
         <v>4</v>
@@ -8666,7 +8666,7 @@
         <v>70</v>
       </c>
       <c r="N158" t="n">
-        <v>680</v>
+        <v>630</v>
       </c>
     </row>
     <row r="159">
@@ -8698,11 +8698,11 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -8718,7 +8718,7 @@
         <v>70</v>
       </c>
       <c r="N159" t="n">
-        <v>490</v>
+        <v>420</v>
       </c>
     </row>
     <row r="160">
@@ -8761,7 +8761,7 @@
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
@@ -8802,18 +8802,18 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J161" t="n">
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" t="n">
         <v>3</v>
@@ -8822,7 +8822,7 @@
         <v>80</v>
       </c>
       <c r="N161" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="162">
@@ -8854,11 +8854,11 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -8874,7 +8874,7 @@
         <v>90</v>
       </c>
       <c r="N162" t="n">
-        <v>490</v>
+        <v>530</v>
       </c>
     </row>
     <row r="163">
@@ -8906,18 +8906,18 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J163" t="n">
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -8926,7 +8926,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="164">
@@ -8958,18 +8958,18 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>660</v>
+        <v>450</v>
       </c>
     </row>
     <row r="165">
@@ -9010,18 +9010,18 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
     </row>
     <row r="166">
@@ -9062,18 +9062,18 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9082,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>490</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167">
@@ -9114,11 +9114,11 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9166,18 +9166,18 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9186,7 +9186,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="169">
@@ -9218,18 +9218,18 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9238,7 +9238,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>642.3</v>
+        <v>442.3</v>
       </c>
     </row>
     <row r="170">
@@ -9270,11 +9270,11 @@
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9290,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="171">
@@ -9322,18 +9322,18 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J171" t="n">
         <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L171" t="n">
         <v>3</v>
@@ -9342,7 +9342,7 @@
         <v>50</v>
       </c>
       <c r="N171" t="n">
-        <v>670</v>
+        <v>660</v>
       </c>
     </row>
     <row r="172">
@@ -9374,18 +9374,18 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
@@ -9394,7 +9394,7 @@
         <v>50</v>
       </c>
       <c r="N172" t="n">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="173">
@@ -9426,18 +9426,18 @@
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J173" t="n">
         <v>1</v>
       </c>
       <c r="K173" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
         <v>3</v>
@@ -9446,7 +9446,7 @@
         <v>50</v>
       </c>
       <c r="N173" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
     </row>
     <row r="174">
@@ -9478,11 +9478,11 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9498,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>540</v>
+        <v>590</v>
       </c>
     </row>
     <row r="175">
@@ -9530,11 +9530,11 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9550,7 +9550,7 @@
         <v>80</v>
       </c>
       <c r="N175" t="n">
-        <v>540</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -9771,20 +9771,20 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
@@ -9792,23 +9792,21 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>1</v>
       </c>
@@ -9819,10 +9817,10 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -9845,7 +9843,9 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -9911,16 +9911,16 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -10058,10 +10058,10 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -10069,30 +10069,30 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -10113,16 +10113,18 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
@@ -10130,21 +10132,17 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,13 +10171,13 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
@@ -10194,9 +10192,7 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -10207,24 +10203,26 @@
         <v>1</v>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
@@ -10241,9 +10239,7 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -10253,25 +10249,27 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
@@ -10304,24 +10302,24 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
         <v>1</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -10341,10 +10339,10 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -10366,10 +10364,10 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10390,13 +10388,13 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
@@ -10404,15 +10402,15 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10428,18 +10426,18 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>1</v>
       </c>
@@ -10450,7 +10448,9 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -10490,13 +10490,13 @@
         <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10512,16 +10512,18 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>1</v>
       </c>
@@ -10548,7 +10550,9 @@
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -10559,10 +10563,10 @@
       <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -10576,17 +10580,15 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10639,13 +10641,9 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -10668,7 +10666,9 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10685,13 +10685,11 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -10700,15 +10698,17 @@
         <v>1</v>
       </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -10728,9 +10728,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -10746,7 +10744,9 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
         <v>1</v>
@@ -10806,7 +10806,9 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
@@ -10819,9 +10821,7 @@
         <v>1</v>
       </c>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
@@ -10834,7 +10834,9 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -10848,11 +10850,11 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -10869,11 +10871,11 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
@@ -10892,10 +10894,10 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -10912,11 +10914,11 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
@@ -10935,22 +10937,22 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
@@ -10982,9 +10984,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>1</v>
       </c>
@@ -11004,7 +11004,9 @@
         <v>1</v>
       </c>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
@@ -11016,7 +11018,9 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
@@ -11025,12 +11029,14 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -11040,9 +11046,7 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
@@ -11055,15 +11059,15 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
@@ -11077,19 +11081,17 @@
       <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
@@ -11102,9 +11104,7 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -11121,9 +11121,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>1</v>
       </c>
@@ -11141,11 +11139,13 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="inlineStr"/>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
@@ -11214,7 +11214,9 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -11230,9 +11232,7 @@
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -11249,28 +11249,30 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
@@ -11278,17 +11280,13 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>1</v>
       </c>
@@ -11315,17 +11313,19 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -11358,13 +11358,13 @@
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
@@ -11386,11 +11386,11 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -11410,10 +11410,10 @@
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
@@ -11450,11 +11450,13 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
@@ -11464,7 +11466,9 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
@@ -11474,11 +11478,13 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -11488,24 +11494,18 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/04_26_schedule_results.xlsx
+++ b/Data/04_26_schedule_results.xlsx
@@ -534,11 +534,11 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,7 +554,7 @@
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3">
@@ -638,11 +638,11 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -658,7 +658,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>610</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5">
@@ -701,7 +701,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>3.5</v>
@@ -710,7 +710,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +753,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>3.5</v>
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7">
@@ -794,18 +794,18 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
         <v>3.5</v>
@@ -814,7 +814,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>610</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8">
@@ -846,18 +846,18 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>3.5</v>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>610</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>3.5</v>
@@ -950,18 +950,18 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
         <v>3.5</v>
@@ -970,7 +970,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11">
@@ -1002,18 +1002,18 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>3.5</v>
@@ -1022,7 +1022,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>610</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12">
@@ -1054,18 +1054,18 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>3.5</v>
@@ -1074,7 +1074,7 @@
         <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>390</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13">
@@ -1106,18 +1106,18 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>3.5</v>
@@ -1126,7 +1126,7 @@
         <v>70</v>
       </c>
       <c r="N13" t="n">
-        <v>620</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14">
@@ -1158,18 +1158,18 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1178,7 +1178,7 @@
         <v>70</v>
       </c>
       <c r="N14" t="n">
-        <v>652.3</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15">
@@ -1210,18 +1210,18 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
         <v>3.5</v>
@@ -1230,7 +1230,7 @@
         <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>400</v>
+        <v>630</v>
       </c>
     </row>
     <row r="16">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1282,7 +1282,7 @@
         <v>70</v>
       </c>
       <c r="N16" t="n">
-        <v>440</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17">
@@ -1314,11 +1314,11 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1377,7 +1377,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19">
@@ -1418,18 +1418,18 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="N19" t="n">
-        <v>610</v>
+        <v>670</v>
       </c>
     </row>
     <row r="20">
@@ -1470,18 +1470,18 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1490,7 +1490,7 @@
         <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>410</v>
+        <v>607.7</v>
       </c>
     </row>
     <row r="21">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>70</v>
       </c>
       <c r="N21" t="n">
-        <v>612.3</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22">
@@ -1574,18 +1574,18 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>410</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23">
@@ -1626,18 +1626,18 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>640</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24">
@@ -1678,18 +1678,18 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1698,7 +1698,7 @@
         <v>70</v>
       </c>
       <c r="N24" t="n">
-        <v>410</v>
+        <v>610</v>
       </c>
     </row>
     <row r="25">
@@ -1730,18 +1730,18 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1750,7 +1750,7 @@
         <v>70</v>
       </c>
       <c r="N25" t="n">
-        <v>600</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26">
@@ -1782,18 +1782,18 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1802,7 +1802,7 @@
         <v>70</v>
       </c>
       <c r="N26" t="n">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27">
@@ -1834,18 +1834,18 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         <v>70</v>
       </c>
       <c r="N27" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28">
@@ -1897,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -1906,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="N28" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="29">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="N29" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30">
@@ -1990,18 +1990,18 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2010,7 +2010,7 @@
         <v>70</v>
       </c>
       <c r="N30" t="n">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31">
@@ -2042,18 +2042,18 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J31" t="n">
         <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2062,7 +2062,7 @@
         <v>70</v>
       </c>
       <c r="N31" t="n">
-        <v>412.3</v>
+        <v>740</v>
       </c>
     </row>
     <row r="32">
@@ -2094,18 +2094,18 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2114,7 +2114,7 @@
         <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>540</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33">
@@ -2146,11 +2146,11 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2166,7 +2166,7 @@
         <v>70</v>
       </c>
       <c r="N33" t="n">
-        <v>410</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="34">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2218,7 +2218,7 @@
         <v>70</v>
       </c>
       <c r="N34" t="n">
-        <v>412.3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35">
@@ -2250,18 +2250,18 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         <v>70</v>
       </c>
       <c r="N35" t="n">
-        <v>420</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="36">
@@ -2302,11 +2302,11 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2322,7 +2322,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
     </row>
     <row r="37">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2374,7 +2374,7 @@
         <v>90</v>
       </c>
       <c r="N37" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="38">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J38" t="n">
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
         <v>3.5</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>460</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39">
@@ -2458,18 +2458,18 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J39" t="n">
         <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>3.5</v>
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>660</v>
+        <v>410</v>
       </c>
     </row>
     <row r="40">
@@ -2510,18 +2510,18 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J40" t="n">
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
         <v>3.5</v>
@@ -2530,7 +2530,7 @@
         <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="41">
@@ -2573,7 +2573,7 @@
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
         <v>3.5</v>
@@ -2582,7 +2582,7 @@
         <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>630</v>
+        <v>660</v>
       </c>
     </row>
     <row r="42">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J42" t="n">
         <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
         <v>3.5</v>
@@ -2634,7 +2634,7 @@
         <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>630</v>
+        <v>670</v>
       </c>
     </row>
     <row r="43">
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
         <v>3.5</v>
@@ -2686,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>540</v>
+        <v>460</v>
       </c>
     </row>
     <row r="44">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L44" t="n">
         <v>3.5</v>
@@ -2738,7 +2738,7 @@
         <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>490</v>
+        <v>660</v>
       </c>
     </row>
     <row r="45">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
         <v>3.5</v>
@@ -2790,7 +2790,7 @@
         <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>490</v>
+        <v>610</v>
       </c>
     </row>
     <row r="46">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L46" t="n">
         <v>3.5</v>
@@ -2842,7 +2842,7 @@
         <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="47">
@@ -2874,18 +2874,18 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J47" t="n">
         <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
         <v>3.5</v>
@@ -2894,7 +2894,7 @@
         <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2946,7 +2946,7 @@
         <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>520</v>
+        <v>590</v>
       </c>
     </row>
     <row r="49">
@@ -2989,7 +2989,7 @@
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>3.5</v>
@@ -2998,7 +2998,7 @@
         <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>650</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50">
@@ -3041,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>3.5</v>
@@ -3050,7 +3050,7 @@
         <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>462.3</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="51">
@@ -3093,7 +3093,7 @@
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L51" t="n">
         <v>3.5</v>
@@ -3102,7 +3102,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="52">
@@ -3145,7 +3145,7 @@
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3154,7 +3154,7 @@
         <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>490</v>
+        <v>660</v>
       </c>
     </row>
     <row r="53">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
         <v>3.5</v>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>490</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
         <v>3.5</v>
@@ -3258,7 +3258,7 @@
         <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>702.3</v>
+        <v>730</v>
       </c>
     </row>
     <row r="55">
@@ -3290,18 +3290,18 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3310,7 +3310,7 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
     </row>
     <row r="56">
@@ -3342,18 +3342,18 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3362,7 +3362,7 @@
         <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="57">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L57" t="n">
         <v>3.5</v>
@@ -3414,7 +3414,7 @@
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>630</v>
+        <v>690</v>
       </c>
     </row>
     <row r="58">
@@ -3446,18 +3446,18 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J58" t="n">
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L58" t="n">
         <v>3.5</v>
@@ -3466,7 +3466,7 @@
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="59">
@@ -3518,7 +3518,7 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>640</v>
+        <v>570</v>
       </c>
     </row>
     <row r="60">
@@ -3550,18 +3550,18 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J60" t="n">
         <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" t="n">
         <v>4</v>
@@ -3570,7 +3570,7 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>460</v>
+        <v>670</v>
       </c>
     </row>
     <row r="61">
@@ -3602,18 +3602,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L61" t="n">
         <v>4</v>
@@ -3622,7 +3622,7 @@
         <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>710</v>
+        <v>730</v>
       </c>
     </row>
     <row r="62">
@@ -3654,18 +3654,18 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J62" t="n">
         <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L62" t="n">
         <v>4</v>
@@ -3706,18 +3706,18 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -3758,18 +3758,18 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -3810,18 +3810,18 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L65" t="n">
         <v>4</v>
@@ -3830,7 +3830,7 @@
         <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>710</v>
+        <v>507.7</v>
       </c>
     </row>
     <row r="66">
@@ -3862,18 +3862,18 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>4</v>
@@ -3882,7 +3882,7 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>690</v>
+        <v>460</v>
       </c>
     </row>
     <row r="67">
@@ -3914,18 +3914,18 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J67" t="n">
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -3934,7 +3934,7 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>710</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68">
@@ -3966,18 +3966,18 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -3986,7 +3986,7 @@
         <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>490</v>
+        <v>720</v>
       </c>
     </row>
     <row r="69">
@@ -4018,18 +4018,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J69" t="n">
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -4038,7 +4038,7 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>460</v>
+        <v>717.7</v>
       </c>
     </row>
     <row r="70">
@@ -4070,18 +4070,18 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J70" t="n">
         <v>2</v>
       </c>
       <c r="K70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L70" t="n">
         <v>4</v>
@@ -4090,7 +4090,7 @@
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>720</v>
+        <v>730</v>
       </c>
     </row>
     <row r="71">
@@ -4122,11 +4122,11 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4142,7 +4142,7 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>690</v>
+        <v>610</v>
       </c>
     </row>
     <row r="72">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4194,7 +4194,7 @@
         <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row r="73">
@@ -4226,11 +4226,11 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4246,7 +4246,7 @@
         <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>480</v>
+        <v>530</v>
       </c>
     </row>
     <row r="74">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4330,11 +4330,11 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4350,7 +4350,7 @@
         <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>572.3</v>
+        <v>610</v>
       </c>
     </row>
     <row r="76">
@@ -4382,11 +4382,11 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4402,7 +4402,7 @@
         <v>40</v>
       </c>
       <c r="N76" t="n">
-        <v>440</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77">
@@ -4434,11 +4434,11 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4454,7 +4454,7 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>502.3</v>
+        <v>530</v>
       </c>
     </row>
     <row r="78">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4506,7 +4506,7 @@
         <v>80</v>
       </c>
       <c r="N78" t="n">
-        <v>530</v>
+        <v>537.7</v>
       </c>
     </row>
     <row r="79">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4558,7 +4558,7 @@
         <v>80</v>
       </c>
       <c r="N79" t="n">
-        <v>420</v>
+        <v>370</v>
       </c>
     </row>
     <row r="80">
@@ -4601,7 +4601,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>660</v>
+        <v>460</v>
       </c>
     </row>
     <row r="81">
@@ -4642,18 +4642,18 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J81" t="n">
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4662,7 +4662,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>662.3</v>
+        <v>470</v>
       </c>
     </row>
     <row r="82">
@@ -4694,18 +4694,18 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>710</v>
+        <v>720</v>
       </c>
     </row>
     <row r="83">
@@ -4746,18 +4746,18 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row r="84">
@@ -4809,7 +4809,7 @@
         <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -4818,7 +4818,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
     </row>
     <row r="85">
@@ -4850,18 +4850,18 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>660</v>
+        <v>730</v>
       </c>
     </row>
     <row r="86">
@@ -4902,18 +4902,18 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>710</v>
+        <v>730</v>
       </c>
     </row>
     <row r="87">
@@ -4954,18 +4954,18 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -4974,7 +4974,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="88">
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>670</v>
+        <v>470</v>
       </c>
     </row>
     <row r="89">
@@ -5069,7 +5069,7 @@
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row r="90">
@@ -5110,11 +5110,11 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>570</v>
+        <v>450</v>
       </c>
     </row>
     <row r="91">
@@ -5162,18 +5162,18 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J91" t="n">
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
         <v>5</v>
@@ -5182,7 +5182,7 @@
         <v>70</v>
       </c>
       <c r="N91" t="n">
-        <v>440</v>
+        <v>470</v>
       </c>
     </row>
     <row r="92">
@@ -5214,18 +5214,18 @@
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J92" t="n">
         <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
         <v>5</v>
@@ -5234,7 +5234,7 @@
         <v>70</v>
       </c>
       <c r="N92" t="n">
-        <v>440</v>
+        <v>630</v>
       </c>
     </row>
     <row r="93">
@@ -5266,18 +5266,18 @@
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J93" t="n">
         <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>5</v>
@@ -5286,7 +5286,7 @@
         <v>70</v>
       </c>
       <c r="N93" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="94">
@@ -5318,18 +5318,18 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J94" t="n">
         <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
         <v>5</v>
@@ -5338,7 +5338,7 @@
         <v>70</v>
       </c>
       <c r="N94" t="n">
-        <v>642.3</v>
+        <v>470</v>
       </c>
     </row>
     <row r="95">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5390,7 +5390,7 @@
         <v>70</v>
       </c>
       <c r="N95" t="n">
-        <v>440</v>
+        <v>470</v>
       </c>
     </row>
     <row r="96">
@@ -5422,11 +5422,11 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5442,7 +5442,7 @@
         <v>70</v>
       </c>
       <c r="N96" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="97">
@@ -5474,18 +5474,18 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L97" t="n">
         <v>5.5</v>
@@ -5494,7 +5494,7 @@
         <v>70</v>
       </c>
       <c r="N97" t="n">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98">
@@ -5526,18 +5526,18 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L98" t="n">
         <v>5.5</v>
@@ -5546,7 +5546,7 @@
         <v>70</v>
       </c>
       <c r="N98" t="n">
-        <v>400</v>
+        <v>540</v>
       </c>
     </row>
     <row r="99">
@@ -5598,7 +5598,7 @@
         <v>70</v>
       </c>
       <c r="N99" t="n">
-        <v>412.3</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="100">
@@ -5650,7 +5650,7 @@
         <v>70</v>
       </c>
       <c r="N100" t="n">
-        <v>610</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101">
@@ -5702,7 +5702,7 @@
         <v>70</v>
       </c>
       <c r="N101" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="102">
@@ -5734,18 +5734,18 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L102" t="n">
         <v>5.5</v>
@@ -5754,7 +5754,7 @@
         <v>70</v>
       </c>
       <c r="N102" t="n">
-        <v>630</v>
+        <v>657.7</v>
       </c>
     </row>
     <row r="103">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L103" t="n">
         <v>5.5</v>
@@ -5806,7 +5806,7 @@
         <v>70</v>
       </c>
       <c r="N103" t="n">
-        <v>600</v>
+        <v>530</v>
       </c>
     </row>
     <row r="104">
@@ -5838,18 +5838,18 @@
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J104" t="n">
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L104" t="n">
         <v>5.5</v>
@@ -5858,7 +5858,7 @@
         <v>70</v>
       </c>
       <c r="N104" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="105">
@@ -5942,11 +5942,11 @@
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5962,7 +5962,7 @@
         <v>70</v>
       </c>
       <c r="N106" t="n">
-        <v>470</v>
+        <v>330</v>
       </c>
     </row>
     <row r="107">
@@ -6005,7 +6005,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L107" t="n">
         <v>4</v>
@@ -6014,7 +6014,7 @@
         <v>70</v>
       </c>
       <c r="N107" t="n">
-        <v>410</v>
+        <v>590</v>
       </c>
     </row>
     <row r="108">
@@ -6046,18 +6046,18 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J108" t="n">
         <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L108" t="n">
         <v>4</v>
@@ -6066,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="N108" t="n">
-        <v>560</v>
+        <v>650</v>
       </c>
     </row>
     <row r="109">
@@ -6098,18 +6098,18 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J109" t="n">
         <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L109" t="n">
         <v>4</v>
@@ -6118,7 +6118,7 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>700</v>
+        <v>610</v>
       </c>
     </row>
     <row r="110">
@@ -6150,18 +6150,18 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J110" t="n">
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L110" t="n">
         <v>4</v>
@@ -6170,7 +6170,7 @@
         <v>70</v>
       </c>
       <c r="N110" t="n">
-        <v>590</v>
+        <v>677.7</v>
       </c>
     </row>
     <row r="111">
@@ -6202,18 +6202,18 @@
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L111" t="n">
         <v>4</v>
@@ -6222,7 +6222,7 @@
         <v>70</v>
       </c>
       <c r="N111" t="n">
-        <v>440</v>
+        <v>570</v>
       </c>
     </row>
     <row r="112">
@@ -6254,18 +6254,18 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
         <v>4</v>
@@ -6274,7 +6274,7 @@
         <v>70</v>
       </c>
       <c r="N112" t="n">
-        <v>712.3</v>
+        <v>360</v>
       </c>
     </row>
     <row r="113">
@@ -6317,7 +6317,7 @@
         <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L113" t="n">
         <v>4</v>
@@ -6326,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="N113" t="n">
-        <v>440</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114">
@@ -6369,7 +6369,7 @@
         <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L114" t="n">
         <v>4</v>
@@ -6421,7 +6421,7 @@
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L115" t="n">
         <v>4</v>
@@ -6430,7 +6430,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>610</v>
+        <v>350</v>
       </c>
     </row>
     <row r="116">
@@ -6462,18 +6462,18 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L116" t="n">
         <v>4</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="117">
@@ -6514,18 +6514,18 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J117" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>4</v>
@@ -6534,7 +6534,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>640</v>
+        <v>540</v>
       </c>
     </row>
     <row r="118">
@@ -6577,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L118" t="n">
         <v>4</v>
@@ -6586,7 +6586,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="119">
@@ -6618,18 +6618,18 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J119" t="n">
         <v>2</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
         <v>4</v>
@@ -6638,7 +6638,7 @@
         <v>80</v>
       </c>
       <c r="N119" t="n">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="120">
@@ -6670,18 +6670,18 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J120" t="n">
         <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
         <v>4</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="N120" t="n">
-        <v>580</v>
+        <v>610</v>
       </c>
     </row>
     <row r="121">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6742,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="122">
@@ -6774,11 +6774,11 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6794,7 +6794,7 @@
         <v>40</v>
       </c>
       <c r="N122" t="n">
-        <v>430</v>
+        <v>510</v>
       </c>
     </row>
     <row r="123">
@@ -6826,15 +6826,15 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -6878,11 +6878,11 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -6898,7 +6898,7 @@
         <v>80</v>
       </c>
       <c r="N124" t="n">
-        <v>530</v>
+        <v>560</v>
       </c>
     </row>
     <row r="125">
@@ -6930,11 +6930,11 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -6950,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="N125" t="n">
-        <v>580</v>
+        <v>587.7</v>
       </c>
     </row>
     <row r="126">
@@ -6982,11 +6982,11 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7002,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="N126" t="n">
-        <v>580</v>
+        <v>617.7</v>
       </c>
     </row>
     <row r="127">
@@ -7034,11 +7034,11 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -7054,7 +7054,7 @@
         <v>80</v>
       </c>
       <c r="N127" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
     </row>
     <row r="128">
@@ -7097,7 +7097,7 @@
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
         <v>3</v>
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>520</v>
+        <v>410</v>
       </c>
     </row>
     <row r="129">
@@ -7149,7 +7149,7 @@
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L129" t="n">
         <v>3</v>
@@ -7201,7 +7201,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>392.3</v>
+        <v>387.7</v>
       </c>
     </row>
     <row r="131">
@@ -7253,7 +7253,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L131" t="n">
         <v>3</v>
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>470</v>
+        <v>550</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L132" t="n">
         <v>3</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="133">
@@ -7346,18 +7346,18 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7366,7 +7366,7 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>730</v>
+        <v>640</v>
       </c>
     </row>
     <row r="134">
@@ -7398,18 +7398,18 @@
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J134" t="n">
         <v>1</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L134" t="n">
         <v>3</v>
@@ -7418,7 +7418,7 @@
         <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>470</v>
+        <v>740</v>
       </c>
     </row>
     <row r="135">
@@ -7470,7 +7470,7 @@
         <v>80</v>
       </c>
       <c r="N135" t="n">
-        <v>410</v>
+        <v>360</v>
       </c>
     </row>
     <row r="136">
@@ -7502,11 +7502,11 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7522,7 +7522,7 @@
         <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>492.3</v>
+        <v>530</v>
       </c>
     </row>
     <row r="137">
@@ -7554,15 +7554,15 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
         <v>100</v>
       </c>
       <c r="N137" t="n">
-        <v>510</v>
+        <v>470</v>
       </c>
     </row>
     <row r="138">
@@ -7606,11 +7606,11 @@
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -7626,7 +7626,7 @@
         <v>80</v>
       </c>
       <c r="N138" t="n">
-        <v>542.3</v>
+        <v>550</v>
       </c>
     </row>
     <row r="139">
@@ -7658,11 +7658,11 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7678,7 +7678,7 @@
         <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>582.3</v>
+        <v>537.7</v>
       </c>
     </row>
     <row r="140">
@@ -7710,18 +7710,18 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J140" t="n">
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -7730,7 +7730,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="141">
@@ -7773,7 +7773,7 @@
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="142">
@@ -7825,7 +7825,7 @@
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="143">
@@ -7877,7 +7877,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -7886,7 +7886,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="144">
@@ -7918,11 +7918,11 @@
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -7970,18 +7970,18 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J145" t="n">
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>540</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146">
@@ -8022,18 +8022,18 @@
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8042,7 +8042,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>540</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="147">
@@ -8074,18 +8074,18 @@
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J147" t="n">
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8094,7 +8094,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>540</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148">
@@ -8137,7 +8137,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8178,18 +8178,18 @@
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J149" t="n">
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8198,7 +8198,7 @@
         <v>50</v>
       </c>
       <c r="N149" t="n">
-        <v>450</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="150">
@@ -8241,7 +8241,7 @@
         <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L150" t="n">
         <v>4</v>
@@ -8250,7 +8250,7 @@
         <v>50</v>
       </c>
       <c r="N150" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
     </row>
     <row r="151">
@@ -8302,7 +8302,7 @@
         <v>50</v>
       </c>
       <c r="N151" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152">
@@ -8334,18 +8334,18 @@
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J152" t="n">
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L152" t="n">
         <v>4</v>
@@ -8354,7 +8354,7 @@
         <v>70</v>
       </c>
       <c r="N152" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
     </row>
     <row r="153">
@@ -8386,18 +8386,18 @@
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J153" t="n">
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L153" t="n">
         <v>4</v>
@@ -8406,7 +8406,7 @@
         <v>70</v>
       </c>
       <c r="N153" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154">
@@ -8438,18 +8438,18 @@
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J154" t="n">
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L154" t="n">
         <v>4</v>
@@ -8458,7 +8458,7 @@
         <v>70</v>
       </c>
       <c r="N154" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155">
@@ -8490,18 +8490,18 @@
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J155" t="n">
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L155" t="n">
         <v>4</v>
@@ -8510,7 +8510,7 @@
         <v>70</v>
       </c>
       <c r="N155" t="n">
-        <v>560</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="156">
@@ -8542,18 +8542,18 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J156" t="n">
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L156" t="n">
         <v>4</v>
@@ -8562,7 +8562,7 @@
         <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>530</v>
+        <v>380</v>
       </c>
     </row>
     <row r="157">
@@ -8594,18 +8594,18 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J157" t="n">
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L157" t="n">
         <v>4</v>
@@ -8614,7 +8614,7 @@
         <v>70</v>
       </c>
       <c r="N157" t="n">
-        <v>430</v>
+        <v>530</v>
       </c>
     </row>
     <row r="158">
@@ -8646,18 +8646,18 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>4</v>
@@ -8666,7 +8666,7 @@
         <v>70</v>
       </c>
       <c r="N158" t="n">
-        <v>630</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159">
@@ -8698,18 +8698,18 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J159" t="n">
         <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L159" t="n">
         <v>4</v>
@@ -8718,7 +8718,7 @@
         <v>70</v>
       </c>
       <c r="N159" t="n">
-        <v>420</v>
+        <v>690</v>
       </c>
     </row>
     <row r="160">
@@ -8750,18 +8750,18 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J160" t="n">
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
@@ -8802,18 +8802,18 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J161" t="n">
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>3</v>
@@ -8854,11 +8854,11 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -8874,7 +8874,7 @@
         <v>90</v>
       </c>
       <c r="N162" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="163">
@@ -8906,18 +8906,18 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J163" t="n">
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -8926,7 +8926,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>510</v>
+        <v>580</v>
       </c>
     </row>
     <row r="164">
@@ -8958,18 +8958,18 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>450</v>
+        <v>510</v>
       </c>
     </row>
     <row r="165">
@@ -9010,18 +9010,18 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
     </row>
     <row r="166">
@@ -9062,18 +9062,18 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9082,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167">
@@ -9114,18 +9114,18 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J167" t="n">
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9134,7 +9134,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="168">
@@ -9166,18 +9166,18 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9186,7 +9186,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>660</v>
+        <v>460</v>
       </c>
     </row>
     <row r="169">
@@ -9218,18 +9218,18 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9238,7 +9238,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>442.3</v>
+        <v>450</v>
       </c>
     </row>
     <row r="170">
@@ -9270,18 +9270,18 @@
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J170" t="n">
         <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L170" t="n">
         <v>3</v>
@@ -9290,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>660</v>
+        <v>667.7</v>
       </c>
     </row>
     <row r="171">
@@ -9322,11 +9322,11 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -9342,7 +9342,7 @@
         <v>50</v>
       </c>
       <c r="N171" t="n">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="172">
@@ -9374,18 +9374,18 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J172" t="n">
         <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
@@ -9394,7 +9394,7 @@
         <v>50</v>
       </c>
       <c r="N172" t="n">
-        <v>680</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173">
@@ -9426,11 +9426,11 @@
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9446,7 +9446,7 @@
         <v>50</v>
       </c>
       <c r="N173" t="n">
-        <v>650</v>
+        <v>620</v>
       </c>
     </row>
     <row r="174">
@@ -9478,18 +9478,18 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J174" t="n">
         <v>2</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" t="n">
         <v>3</v>
@@ -9498,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>590</v>
+        <v>610</v>
       </c>
     </row>
     <row r="175">
@@ -9530,18 +9530,18 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J175" t="n">
         <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
@@ -9550,7 +9550,7 @@
         <v>80</v>
       </c>
       <c r="N175" t="n">
-        <v>510</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -9771,20 +9771,20 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
         <v>1</v>
       </c>
@@ -9794,13 +9794,13 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9820,7 +9820,9 @@
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -9835,17 +9837,15 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -9854,9 +9854,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -9867,9 +9865,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9879,7 +9875,9 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -9892,7 +9890,9 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9911,13 +9911,15 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
@@ -9933,9 +9935,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -10027,15 +10027,17 @@
         <v>1</v>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -10043,15 +10045,11 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -10077,14 +10075,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -10104,20 +10102,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -10135,13 +10135,13 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -10192,7 +10192,9 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -10203,33 +10205,31 @@
         <v>1</v>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -10239,21 +10239,23 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -10267,9 +10269,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
@@ -10286,9 +10286,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -10320,47 +10318,47 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -10421,26 +10419,24 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -10490,13 +10486,13 @@
         <v>1</v>
       </c>
       <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10505,7 +10501,9 @@
       <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -10524,9 +10522,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -10550,22 +10546,20 @@
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -10588,7 +10582,9 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10641,16 +10637,18 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -10665,10 +10663,10 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10686,26 +10684,26 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
@@ -10747,7 +10745,9 @@
       <c r="Y25" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
       <c r="AA25" t="n">
         <v>1</v>
       </c>
@@ -10798,7 +10798,9 @@
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -10806,20 +10808,20 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -10827,16 +10829,12 @@
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -10851,10 +10849,10 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -10873,13 +10871,13 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -10938,18 +10936,16 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="n">
         <v>1</v>
       </c>
@@ -10957,15 +10953,17 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
       <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -10984,29 +10982,27 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
@@ -11023,16 +11019,14 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>1</v>
@@ -11044,7 +11038,9 @@
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -11065,9 +11061,7 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
@@ -11078,10 +11072,10 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -11096,7 +11090,9 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
@@ -11104,24 +11100,28 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
@@ -11129,12 +11129,12 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
@@ -11143,9 +11143,7 @@
         <v>1</v>
       </c>
       <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
@@ -11204,31 +11202,29 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
@@ -11239,23 +11235,21 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -11263,14 +11257,16 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
@@ -11331,17 +11327,19 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
@@ -11358,53 +11356,53 @@
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
@@ -11438,11 +11436,13 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
@@ -11450,9 +11450,7 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="n">
         <v>1</v>
@@ -11469,9 +11467,7 @@
       <c r="B42" t="n">
         <v>1</v>
       </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -11482,30 +11478,34 @@
       <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+      <c r="Y42" t="n">
+        <v>1</v>
+      </c>
       <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/04_26_schedule_results.xlsx
+++ b/Data/04_26_schedule_results.xlsx
@@ -534,11 +534,11 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,7 +554,7 @@
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>540</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3">
@@ -586,15 +586,15 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4">
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>3.5</v>
@@ -658,7 +658,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>410</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5">
@@ -690,18 +690,18 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
         <v>3.5</v>
@@ -710,7 +710,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>440</v>
+        <v>607.7</v>
       </c>
     </row>
     <row r="6">
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7">
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>3.5</v>
@@ -814,7 +814,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8">
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>620</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9">
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>3.5</v>
@@ -918,7 +918,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>640</v>
+        <v>690</v>
       </c>
     </row>
     <row r="10">
@@ -950,18 +950,18 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>3.5</v>
@@ -970,7 +970,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>610</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11">
@@ -1002,18 +1002,18 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>3.5</v>
@@ -1022,7 +1022,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>600</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12">
@@ -1054,18 +1054,18 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
         <v>3.5</v>
@@ -1074,7 +1074,7 @@
         <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>612.3</v>
+        <v>680</v>
       </c>
     </row>
     <row r="13">
@@ -1117,7 +1117,7 @@
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>3.5</v>
@@ -1126,7 +1126,7 @@
         <v>70</v>
       </c>
       <c r="N13" t="n">
-        <v>620</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14">
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1178,7 +1178,7 @@
         <v>70</v>
       </c>
       <c r="N14" t="n">
-        <v>510</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
         <v>3.5</v>
@@ -1230,7 +1230,7 @@
         <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="16">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1282,7 +1282,7 @@
         <v>70</v>
       </c>
       <c r="N16" t="n">
-        <v>410</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17">
@@ -1314,11 +1314,11 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1334,7 +1334,7 @@
         <v>80</v>
       </c>
       <c r="N17" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18">
@@ -1377,7 +1377,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>650</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19">
@@ -1418,18 +1418,18 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1470,18 +1470,18 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1490,7 +1490,7 @@
         <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>610</v>
+        <v>520</v>
       </c>
     </row>
     <row r="21">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>70</v>
       </c>
       <c r="N21" t="n">
-        <v>612.3</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22">
@@ -1574,11 +1574,11 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1594,7 +1594,7 @@
         <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>640</v>
+        <v>610</v>
       </c>
     </row>
     <row r="23">
@@ -1626,18 +1626,18 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="24">
@@ -1678,11 +1678,11 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1782,18 +1782,18 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1802,7 +1802,7 @@
         <v>70</v>
       </c>
       <c r="N26" t="n">
-        <v>440</v>
+        <v>530</v>
       </c>
     </row>
     <row r="27">
@@ -1834,18 +1834,18 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         <v>70</v>
       </c>
       <c r="N27" t="n">
-        <v>640</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28">
@@ -1886,18 +1886,18 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -1906,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="N28" t="n">
-        <v>410</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="N29" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30">
@@ -1990,18 +1990,18 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2010,7 +2010,7 @@
         <v>70</v>
       </c>
       <c r="N30" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31">
@@ -2042,18 +2042,18 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J31" t="n">
         <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2062,7 +2062,7 @@
         <v>70</v>
       </c>
       <c r="N31" t="n">
-        <v>412.3</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32">
@@ -2094,18 +2094,18 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2114,7 +2114,7 @@
         <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>580</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="33">
@@ -2146,18 +2146,18 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2166,7 +2166,7 @@
         <v>70</v>
       </c>
       <c r="N33" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2218,7 +2218,7 @@
         <v>70</v>
       </c>
       <c r="N34" t="n">
-        <v>390</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35">
@@ -2250,18 +2250,18 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         <v>70</v>
       </c>
       <c r="N35" t="n">
-        <v>410</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="36">
@@ -2302,11 +2302,11 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2322,7 +2322,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
     </row>
     <row r="37">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2374,7 +2374,7 @@
         <v>90</v>
       </c>
       <c r="N37" t="n">
-        <v>510</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J38" t="n">
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>3.5</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>510</v>
+        <v>410</v>
       </c>
     </row>
     <row r="39">
@@ -2458,11 +2458,11 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>460</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40">
@@ -2510,18 +2510,18 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J40" t="n">
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L40" t="n">
         <v>3.5</v>
@@ -2530,7 +2530,7 @@
         <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>660</v>
+        <v>670</v>
       </c>
     </row>
     <row r="41">
@@ -2562,11 +2562,11 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2582,7 +2582,7 @@
         <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
     </row>
     <row r="42">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J42" t="n">
         <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
         <v>3.5</v>
@@ -2634,7 +2634,7 @@
         <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>650</v>
+        <v>610</v>
       </c>
     </row>
     <row r="43">
@@ -2666,18 +2666,18 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
         <v>3.5</v>
@@ -2686,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="44">
@@ -2729,7 +2729,7 @@
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L44" t="n">
         <v>3.5</v>
@@ -2738,7 +2738,7 @@
         <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
     </row>
     <row r="45">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L45" t="n">
         <v>3.5</v>
@@ -2790,7 +2790,7 @@
         <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>660</v>
+        <v>460</v>
       </c>
     </row>
     <row r="46">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L46" t="n">
         <v>3.5</v>
@@ -2842,7 +2842,7 @@
         <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>540</v>
+        <v>710</v>
       </c>
     </row>
     <row r="47">
@@ -2874,11 +2874,11 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2894,7 +2894,7 @@
         <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="48">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2946,7 +2946,7 @@
         <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>470</v>
+        <v>590</v>
       </c>
     </row>
     <row r="49">
@@ -2989,7 +2989,7 @@
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>3.5</v>
@@ -2998,7 +2998,7 @@
         <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>700</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50">
@@ -3030,18 +3030,18 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
         <v>3.5</v>
@@ -3050,7 +3050,7 @@
         <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>710</v>
+        <v>660</v>
       </c>
     </row>
     <row r="51">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>3.5</v>
@@ -3102,7 +3102,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>740</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="52">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3154,7 +3154,7 @@
         <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>690</v>
+        <v>710</v>
       </c>
     </row>
     <row r="53">
@@ -3186,18 +3186,18 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L53" t="n">
         <v>3.5</v>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>462.3</v>
+        <v>660</v>
       </c>
     </row>
     <row r="54">
@@ -3238,18 +3238,18 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L54" t="n">
         <v>3.5</v>
@@ -3258,7 +3258,7 @@
         <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>490</v>
+        <v>680</v>
       </c>
     </row>
     <row r="55">
@@ -3301,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3310,7 +3310,7 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>510</v>
+        <v>460</v>
       </c>
     </row>
     <row r="56">
@@ -3342,18 +3342,18 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3362,7 +3362,7 @@
         <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>530</v>
+        <v>677.7</v>
       </c>
     </row>
     <row r="57">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57" t="n">
         <v>3.5</v>
@@ -3414,7 +3414,7 @@
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>462.3</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58">
@@ -3446,18 +3446,18 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L58" t="n">
         <v>3.5</v>
@@ -3466,7 +3466,7 @@
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>640</v>
+        <v>690</v>
       </c>
     </row>
     <row r="59">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3518,7 +3518,7 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>640</v>
+        <v>570</v>
       </c>
     </row>
     <row r="60">
@@ -3550,11 +3550,11 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3570,7 +3570,7 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>462.3</v>
+        <v>480</v>
       </c>
     </row>
     <row r="61">
@@ -3602,18 +3602,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L61" t="n">
         <v>4</v>
@@ -3622,7 +3622,7 @@
         <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="62">
@@ -3654,11 +3654,11 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3674,7 +3674,7 @@
         <v>50</v>
       </c>
       <c r="N62" t="n">
-        <v>690</v>
+        <v>720</v>
       </c>
     </row>
     <row r="63">
@@ -3706,18 +3706,18 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -3726,7 +3726,7 @@
         <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>760</v>
+        <v>710</v>
       </c>
     </row>
     <row r="64">
@@ -3758,18 +3758,18 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -3778,7 +3778,7 @@
         <v>50</v>
       </c>
       <c r="N64" t="n">
-        <v>740</v>
+        <v>510</v>
       </c>
     </row>
     <row r="65">
@@ -3810,18 +3810,18 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L65" t="n">
         <v>4</v>
@@ -3830,7 +3830,7 @@
         <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>490</v>
+        <v>760</v>
       </c>
     </row>
     <row r="66">
@@ -3862,18 +3862,18 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>4</v>
@@ -3882,7 +3882,7 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>710</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67">
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -3934,7 +3934,7 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>670</v>
+        <v>760</v>
       </c>
     </row>
     <row r="68">
@@ -3977,7 +3977,7 @@
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -3986,7 +3986,7 @@
         <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="69">
@@ -4018,18 +4018,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J69" t="n">
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -4038,7 +4038,7 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>470</v>
+        <v>740</v>
       </c>
     </row>
     <row r="70">
@@ -4081,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>4</v>
@@ -4090,7 +4090,7 @@
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="71">
@@ -4133,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4142,7 +4142,7 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>580</v>
+        <v>740</v>
       </c>
     </row>
     <row r="72">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4194,7 +4194,7 @@
         <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
     </row>
     <row r="73">
@@ -4226,11 +4226,11 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4246,7 +4246,7 @@
         <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>522.3</v>
+        <v>530</v>
       </c>
     </row>
     <row r="74">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4298,7 +4298,7 @@
         <v>40</v>
       </c>
       <c r="N74" t="n">
-        <v>480</v>
+        <v>497.7</v>
       </c>
     </row>
     <row r="75">
@@ -4330,11 +4330,11 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4350,7 +4350,7 @@
         <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>530</v>
+        <v>620</v>
       </c>
     </row>
     <row r="76">
@@ -4382,11 +4382,11 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4402,7 +4402,7 @@
         <v>40</v>
       </c>
       <c r="N76" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="77">
@@ -4434,11 +4434,11 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4454,7 +4454,7 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="78">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4506,7 +4506,7 @@
         <v>80</v>
       </c>
       <c r="N78" t="n">
-        <v>570</v>
+        <v>540</v>
       </c>
     </row>
     <row r="79">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4558,7 +4558,7 @@
         <v>80</v>
       </c>
       <c r="N79" t="n">
-        <v>450</v>
+        <v>370</v>
       </c>
     </row>
     <row r="80">
@@ -4590,18 +4590,18 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>460</v>
+        <v>670</v>
       </c>
     </row>
     <row r="81">
@@ -4653,7 +4653,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4662,7 +4662,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>660</v>
+        <v>460</v>
       </c>
     </row>
     <row r="82">
@@ -4694,11 +4694,11 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83">
@@ -4746,18 +4746,18 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>670</v>
+        <v>740</v>
       </c>
     </row>
     <row r="84">
@@ -4798,18 +4798,18 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J84" t="n">
         <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -4818,7 +4818,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="85">
@@ -4850,18 +4850,18 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="86">
@@ -4902,18 +4902,18 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>662.3</v>
+        <v>630</v>
       </c>
     </row>
     <row r="87">
@@ -4954,18 +4954,18 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -4974,7 +4974,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>610</v>
+        <v>710</v>
       </c>
     </row>
     <row r="88">
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>630</v>
+        <v>730</v>
       </c>
     </row>
     <row r="89">
@@ -5058,18 +5058,18 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row r="90">
@@ -5110,18 +5110,18 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J90" t="n">
         <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>3</v>
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>630</v>
+        <v>450</v>
       </c>
     </row>
     <row r="91">
@@ -5162,18 +5162,18 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J91" t="n">
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>5</v>
@@ -5182,7 +5182,7 @@
         <v>70</v>
       </c>
       <c r="N91" t="n">
-        <v>592.3</v>
+        <v>470</v>
       </c>
     </row>
     <row r="92">
@@ -5214,18 +5214,18 @@
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J92" t="n">
         <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
         <v>5</v>
@@ -5234,7 +5234,7 @@
         <v>70</v>
       </c>
       <c r="N92" t="n">
-        <v>412.3</v>
+        <v>620</v>
       </c>
     </row>
     <row r="93">
@@ -5266,11 +5266,11 @@
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5286,7 +5286,7 @@
         <v>70</v>
       </c>
       <c r="N93" t="n">
-        <v>420</v>
+        <v>470</v>
       </c>
     </row>
     <row r="94">
@@ -5318,11 +5318,11 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5338,7 +5338,7 @@
         <v>70</v>
       </c>
       <c r="N94" t="n">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row r="95">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5390,7 +5390,7 @@
         <v>70</v>
       </c>
       <c r="N95" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
     </row>
     <row r="96">
@@ -5422,11 +5422,11 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5442,7 +5442,7 @@
         <v>70</v>
       </c>
       <c r="N96" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="97">
@@ -5485,7 +5485,7 @@
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
         <v>5.5</v>
@@ -5494,7 +5494,7 @@
         <v>70</v>
       </c>
       <c r="N97" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98">
@@ -5526,18 +5526,18 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L98" t="n">
         <v>5.5</v>
@@ -5546,7 +5546,7 @@
         <v>70</v>
       </c>
       <c r="N98" t="n">
-        <v>570</v>
+        <v>610</v>
       </c>
     </row>
     <row r="99">
@@ -5578,18 +5578,18 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J99" t="n">
         <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L99" t="n">
         <v>5.5</v>
@@ -5598,7 +5598,7 @@
         <v>70</v>
       </c>
       <c r="N99" t="n">
-        <v>412.3</v>
+        <v>530</v>
       </c>
     </row>
     <row r="100">
@@ -5630,18 +5630,18 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J100" t="n">
         <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>5.5</v>
@@ -5650,7 +5650,7 @@
         <v>70</v>
       </c>
       <c r="N100" t="n">
-        <v>600</v>
+        <v>407.7</v>
       </c>
     </row>
     <row r="101">
@@ -5682,11 +5682,11 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5702,7 +5702,7 @@
         <v>70</v>
       </c>
       <c r="N101" t="n">
-        <v>440</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102">
@@ -5734,18 +5734,18 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L102" t="n">
         <v>5.5</v>
@@ -5754,7 +5754,7 @@
         <v>70</v>
       </c>
       <c r="N102" t="n">
-        <v>610</v>
+        <v>430</v>
       </c>
     </row>
     <row r="103">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L103" t="n">
         <v>5.5</v>
@@ -5806,7 +5806,7 @@
         <v>70</v>
       </c>
       <c r="N103" t="n">
-        <v>580</v>
+        <v>530</v>
       </c>
     </row>
     <row r="104">
@@ -5838,11 +5838,11 @@
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5890,18 +5890,18 @@
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J105" t="n">
         <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L105" t="n">
         <v>5.5</v>
@@ -5910,7 +5910,7 @@
         <v>70</v>
       </c>
       <c r="N105" t="n">
-        <v>390</v>
+        <v>520</v>
       </c>
     </row>
     <row r="106">
@@ -5942,11 +5942,11 @@
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5962,7 +5962,7 @@
         <v>70</v>
       </c>
       <c r="N106" t="n">
-        <v>480</v>
+        <v>330</v>
       </c>
     </row>
     <row r="107">
@@ -6014,7 +6014,7 @@
         <v>70</v>
       </c>
       <c r="N107" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
     </row>
     <row r="108">
@@ -6046,18 +6046,18 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J108" t="n">
         <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L108" t="n">
         <v>4</v>
@@ -6066,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="N108" t="n">
-        <v>730</v>
+        <v>600</v>
       </c>
     </row>
     <row r="109">
@@ -6109,7 +6109,7 @@
         <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L109" t="n">
         <v>4</v>
@@ -6118,7 +6118,7 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>682.3</v>
+        <v>677.7</v>
       </c>
     </row>
     <row r="110">
@@ -6161,7 +6161,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L110" t="n">
         <v>4</v>
@@ -6170,7 +6170,7 @@
         <v>70</v>
       </c>
       <c r="N110" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
     </row>
     <row r="111">
@@ -6213,7 +6213,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L111" t="n">
         <v>4</v>
@@ -6222,7 +6222,7 @@
         <v>70</v>
       </c>
       <c r="N111" t="n">
-        <v>440</v>
+        <v>530</v>
       </c>
     </row>
     <row r="112">
@@ -6254,18 +6254,18 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
         <v>4</v>
@@ -6274,7 +6274,7 @@
         <v>70</v>
       </c>
       <c r="N112" t="n">
-        <v>662.3</v>
+        <v>360</v>
       </c>
     </row>
     <row r="113">
@@ -6306,11 +6306,11 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6326,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="N113" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
     </row>
     <row r="114">
@@ -6358,11 +6358,11 @@
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6378,7 +6378,7 @@
         <v>70</v>
       </c>
       <c r="N114" t="n">
-        <v>410</v>
+        <v>350</v>
       </c>
     </row>
     <row r="115">
@@ -6421,7 +6421,7 @@
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L115" t="n">
         <v>4</v>
@@ -6430,7 +6430,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
     </row>
     <row r="116">
@@ -6473,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>4</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>760</v>
+        <v>540</v>
       </c>
     </row>
     <row r="117">
@@ -6525,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L117" t="n">
         <v>4</v>
@@ -6534,7 +6534,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="118">
@@ -6577,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L118" t="n">
         <v>4</v>
@@ -6618,11 +6618,11 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6638,7 +6638,7 @@
         <v>80</v>
       </c>
       <c r="N119" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="120">
@@ -6670,11 +6670,11 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="N120" t="n">
-        <v>660</v>
+        <v>577.7</v>
       </c>
     </row>
     <row r="121">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6742,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>570</v>
+        <v>620</v>
       </c>
     </row>
     <row r="122">
@@ -6774,11 +6774,11 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6794,7 +6794,7 @@
         <v>40</v>
       </c>
       <c r="N122" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="123">
@@ -6826,11 +6826,11 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6846,7 +6846,7 @@
         <v>90</v>
       </c>
       <c r="N123" t="n">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="124">
@@ -6878,18 +6878,18 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J124" t="n">
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
@@ -6898,7 +6898,7 @@
         <v>80</v>
       </c>
       <c r="N124" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="125">
@@ -6930,18 +6930,18 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J125" t="n">
         <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" t="n">
         <v>3</v>
@@ -6950,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="N125" t="n">
-        <v>542.3</v>
+        <v>660</v>
       </c>
     </row>
     <row r="126">
@@ -6982,11 +6982,11 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7002,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="N126" t="n">
-        <v>570</v>
+        <v>660</v>
       </c>
     </row>
     <row r="127">
@@ -7034,18 +7034,18 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7054,7 +7054,7 @@
         <v>80</v>
       </c>
       <c r="N127" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
     </row>
     <row r="128">
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="129">
@@ -7149,7 +7149,7 @@
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L129" t="n">
         <v>3</v>
@@ -7158,7 +7158,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="130">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>392.3</v>
+        <v>450</v>
       </c>
     </row>
     <row r="131">
@@ -7242,18 +7242,18 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J131" t="n">
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L131" t="n">
         <v>3</v>
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>630</v>
+        <v>790</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L132" t="n">
         <v>3</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>490</v>
+        <v>387.7</v>
       </c>
     </row>
     <row r="133">
@@ -7346,11 +7346,11 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7366,7 +7366,7 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
     </row>
     <row r="134">
@@ -7398,11 +7398,11 @@
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7418,7 +7418,7 @@
         <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="135">
@@ -7470,7 +7470,7 @@
         <v>80</v>
       </c>
       <c r="N135" t="n">
-        <v>410</v>
+        <v>360</v>
       </c>
     </row>
     <row r="136">
@@ -7554,15 +7554,15 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
         <v>100</v>
       </c>
       <c r="N137" t="n">
-        <v>520</v>
+        <v>470</v>
       </c>
     </row>
     <row r="138">
@@ -7606,18 +7606,18 @@
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J138" t="n">
         <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" t="n">
         <v>4</v>
@@ -7626,7 +7626,7 @@
         <v>80</v>
       </c>
       <c r="N138" t="n">
-        <v>542.3</v>
+        <v>550</v>
       </c>
     </row>
     <row r="139">
@@ -7658,18 +7658,18 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J139" t="n">
         <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>4</v>
@@ -7678,7 +7678,7 @@
         <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>550</v>
+        <v>537.7</v>
       </c>
     </row>
     <row r="140">
@@ -7721,7 +7721,7 @@
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -7730,7 +7730,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>460</v>
+        <v>570</v>
       </c>
     </row>
     <row r="141">
@@ -7773,7 +7773,7 @@
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>490</v>
+        <v>470</v>
       </c>
     </row>
     <row r="142">
@@ -7814,18 +7814,18 @@
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="143">
@@ -7866,18 +7866,18 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J143" t="n">
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -7886,7 +7886,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>590</v>
+        <v>460</v>
       </c>
     </row>
     <row r="144">
@@ -7918,11 +7918,11 @@
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -7938,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="N144" t="n">
-        <v>490</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145">
@@ -7981,7 +7981,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>490</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146">
@@ -8085,7 +8085,7 @@
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8094,7 +8094,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="148">
@@ -8137,7 +8137,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8146,7 +8146,7 @@
         <v>50</v>
       </c>
       <c r="N148" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="149">
@@ -8178,18 +8178,18 @@
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J149" t="n">
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8198,7 +8198,7 @@
         <v>50</v>
       </c>
       <c r="N149" t="n">
-        <v>560</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="150">
@@ -8230,18 +8230,18 @@
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J150" t="n">
         <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L150" t="n">
         <v>4</v>
@@ -8250,7 +8250,7 @@
         <v>50</v>
       </c>
       <c r="N150" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
     </row>
     <row r="151">
@@ -8282,11 +8282,11 @@
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -8302,7 +8302,7 @@
         <v>50</v>
       </c>
       <c r="N151" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152">
@@ -8345,7 +8345,7 @@
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L152" t="n">
         <v>4</v>
@@ -8354,7 +8354,7 @@
         <v>70</v>
       </c>
       <c r="N152" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153">
@@ -8397,7 +8397,7 @@
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L153" t="n">
         <v>4</v>
@@ -8406,7 +8406,7 @@
         <v>70</v>
       </c>
       <c r="N153" t="n">
-        <v>590</v>
+        <v>430</v>
       </c>
     </row>
     <row r="154">
@@ -8449,7 +8449,7 @@
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L154" t="n">
         <v>4</v>
@@ -8490,18 +8490,18 @@
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J155" t="n">
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L155" t="n">
         <v>4</v>
@@ -8510,7 +8510,7 @@
         <v>70</v>
       </c>
       <c r="N155" t="n">
-        <v>690</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="156">
@@ -8542,18 +8542,18 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J156" t="n">
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L156" t="n">
         <v>4</v>
@@ -8562,7 +8562,7 @@
         <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>462.3</v>
+        <v>380</v>
       </c>
     </row>
     <row r="157">
@@ -8594,18 +8594,18 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J157" t="n">
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L157" t="n">
         <v>4</v>
@@ -8614,7 +8614,7 @@
         <v>70</v>
       </c>
       <c r="N157" t="n">
-        <v>420</v>
+        <v>750</v>
       </c>
     </row>
     <row r="158">
@@ -8646,18 +8646,18 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>4</v>
@@ -8666,7 +8666,7 @@
         <v>70</v>
       </c>
       <c r="N158" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159">
@@ -8698,18 +8698,18 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J159" t="n">
         <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L159" t="n">
         <v>4</v>
@@ -8718,7 +8718,7 @@
         <v>70</v>
       </c>
       <c r="N159" t="n">
-        <v>590</v>
+        <v>690</v>
       </c>
     </row>
     <row r="160">
@@ -8750,11 +8750,11 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8770,7 +8770,7 @@
         <v>80</v>
       </c>
       <c r="N160" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="161">
@@ -8802,11 +8802,11 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -8854,11 +8854,11 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -8874,7 +8874,7 @@
         <v>90</v>
       </c>
       <c r="N162" t="n">
-        <v>490</v>
+        <v>540</v>
       </c>
     </row>
     <row r="163">
@@ -8906,11 +8906,11 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -8926,7 +8926,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
     </row>
     <row r="164">
@@ -8958,18 +8958,18 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>420</v>
+        <v>690</v>
       </c>
     </row>
     <row r="165">
@@ -9010,18 +9010,18 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>640</v>
+        <v>530</v>
       </c>
     </row>
     <row r="166">
@@ -9073,7 +9073,7 @@
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9082,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>530</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167">
@@ -9114,18 +9114,18 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J167" t="n">
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9134,7 +9134,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>710</v>
+        <v>480</v>
       </c>
     </row>
     <row r="168">
@@ -9166,18 +9166,18 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9186,7 +9186,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>650</v>
+        <v>410</v>
       </c>
     </row>
     <row r="169">
@@ -9218,18 +9218,18 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9270,18 +9270,18 @@
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J170" t="n">
         <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L170" t="n">
         <v>3</v>
@@ -9290,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>440</v>
+        <v>627.7</v>
       </c>
     </row>
     <row r="171">
@@ -9322,18 +9322,18 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L171" t="n">
         <v>3</v>
@@ -9342,7 +9342,7 @@
         <v>50</v>
       </c>
       <c r="N171" t="n">
-        <v>690</v>
+        <v>600</v>
       </c>
     </row>
     <row r="172">
@@ -9374,15 +9374,15 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="n">
         <v>10</v>
@@ -9394,7 +9394,7 @@
         <v>50</v>
       </c>
       <c r="N172" t="n">
-        <v>570</v>
+        <v>690</v>
       </c>
     </row>
     <row r="173">
@@ -9446,7 +9446,7 @@
         <v>50</v>
       </c>
       <c r="N173" t="n">
-        <v>530</v>
+        <v>620</v>
       </c>
     </row>
     <row r="174">
@@ -9478,18 +9478,18 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J174" t="n">
         <v>2</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" t="n">
         <v>3</v>
@@ -9498,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>570</v>
+        <v>540</v>
       </c>
     </row>
     <row r="175">
@@ -9530,18 +9530,18 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J175" t="n">
         <v>2</v>
       </c>
       <c r="K175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
@@ -9550,7 +9550,7 @@
         <v>80</v>
       </c>
       <c r="N175" t="n">
-        <v>530</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -9771,18 +9771,16 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
@@ -9800,15 +9798,15 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>1</v>
       </c>
@@ -9827,7 +9825,9 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>1</v>
@@ -9837,10 +9837,10 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -9851,12 +9851,8 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -9866,7 +9862,9 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -9876,10 +9874,10 @@
         <v>1</v>
       </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -9892,7 +9890,9 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9911,16 +9911,18 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -9933,9 +9935,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -10014,9 +10014,7 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -10026,16 +10024,18 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -10049,19 +10049,19 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -10069,10 +10069,10 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -10089,10 +10089,10 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -10103,14 +10103,12 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -10118,16 +10116,18 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -10141,10 +10141,10 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10208,14 +10208,16 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -10232,9 +10234,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10253,20 +10253,22 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -10279,20 +10281,18 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -10314,16 +10314,16 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
         <v>1</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -10344,28 +10344,30 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
       <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
@@ -10383,12 +10385,12 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -10418,31 +10420,31 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
@@ -10450,16 +10452,14 @@
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10526,9 +10526,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -10544,7 +10542,9 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -10562,17 +10562,15 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>1</v>
@@ -10590,7 +10588,9 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10643,10 +10643,10 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
@@ -10654,7 +10654,9 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -10669,9 +10671,7 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -10689,24 +10689,16 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -10732,9 +10724,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -10802,20 +10792,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -10828,11 +10820,11 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
       <c r="Z27" t="n">
         <v>1</v>
       </c>
@@ -10875,22 +10867,24 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -10918,9 +10912,7 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -10941,35 +10933,35 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -10980,9 +10972,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -10997,10 +10987,10 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -11008,7 +10998,9 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
       <c r="Z31" t="n">
         <v>1</v>
       </c>
@@ -11041,11 +11033,11 @@
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -11069,12 +11061,12 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -11084,18 +11076,18 @@
         <v>1</v>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
@@ -11108,7 +11100,9 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -11133,10 +11127,10 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
         <v>1</v>
@@ -11145,15 +11139,17 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11204,16 +11200,18 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>1</v>
       </c>
@@ -11221,9 +11219,7 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="n">
-        <v>1</v>
-      </c>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
@@ -11233,14 +11229,20 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -11249,16 +11251,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
         <v>1</v>
       </c>
@@ -11269,16 +11269,14 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -11287,7 +11285,9 @@
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -11304,42 +11304,42 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
@@ -11347,9 +11347,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -11360,35 +11358,35 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>1</v>
@@ -11396,7 +11394,9 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -11407,17 +11407,15 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -11441,10 +11439,10 @@
       <c r="Q41" t="n">
         <v>1</v>
       </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
@@ -11453,10 +11451,10 @@
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
@@ -11477,7 +11475,9 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
       <c r="L42" t="n">
         <v>1</v>
       </c>
@@ -11485,13 +11485,11 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -11499,7 +11497,9 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>

--- a/Data/04_26_schedule_results.xlsx
+++ b/Data/04_26_schedule_results.xlsx
@@ -534,11 +534,11 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,7 +554,7 @@
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>610</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -586,15 +586,15 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>520</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4">
@@ -638,11 +638,11 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -658,7 +658,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="5">
@@ -690,18 +690,18 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>3.5</v>
@@ -710,7 +710,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>607.7</v>
+        <v>650</v>
       </c>
     </row>
     <row r="6">
@@ -742,18 +742,18 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>3.5</v>
@@ -762,7 +762,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>410</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7">
@@ -794,18 +794,18 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>3.5</v>
@@ -814,7 +814,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>380</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8">
@@ -846,18 +846,18 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>3.5</v>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>690</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9">
@@ -898,18 +898,18 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>3.5</v>
@@ -918,7 +918,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>690</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10">
@@ -950,18 +950,18 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>3.5</v>
@@ -970,7 +970,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -1002,18 +1002,18 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>3.5</v>
@@ -1022,7 +1022,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>580</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12">
@@ -1054,18 +1054,18 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>3.5</v>
@@ -1074,7 +1074,7 @@
         <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>680</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="13">
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1178,7 +1178,7 @@
         <v>70</v>
       </c>
       <c r="N14" t="n">
-        <v>640</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15">
@@ -1282,7 +1282,7 @@
         <v>70</v>
       </c>
       <c r="N16" t="n">
-        <v>490</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17">
@@ -1314,11 +1314,11 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1334,7 +1334,7 @@
         <v>80</v>
       </c>
       <c r="N17" t="n">
-        <v>510</v>
+        <v>620</v>
       </c>
     </row>
     <row r="18">
@@ -1377,7 +1377,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1418,18 +1418,18 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="N19" t="n">
-        <v>610</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20">
@@ -1490,7 +1490,7 @@
         <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>70</v>
       </c>
       <c r="N21" t="n">
-        <v>450</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22">
@@ -1585,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>610</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23">
@@ -1626,18 +1626,18 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24">
@@ -1678,18 +1678,18 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1698,7 +1698,7 @@
         <v>70</v>
       </c>
       <c r="N24" t="n">
-        <v>410</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1750,7 +1750,7 @@
         <v>70</v>
       </c>
       <c r="N25" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26">
@@ -1782,18 +1782,18 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1802,7 +1802,7 @@
         <v>70</v>
       </c>
       <c r="N26" t="n">
-        <v>530</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27">
@@ -1834,18 +1834,18 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         <v>70</v>
       </c>
       <c r="N27" t="n">
-        <v>440</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28">
@@ -1886,18 +1886,18 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -1906,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="N28" t="n">
-        <v>680</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="N29" t="n">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="30">
@@ -1990,18 +1990,18 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2010,7 +2010,7 @@
         <v>70</v>
       </c>
       <c r="N30" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31">
@@ -2042,18 +2042,18 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J31" t="n">
         <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2062,7 +2062,7 @@
         <v>70</v>
       </c>
       <c r="N31" t="n">
-        <v>450</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="32">
@@ -2094,18 +2094,18 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2114,7 +2114,7 @@
         <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>407.7</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33">
@@ -2146,11 +2146,11 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2166,7 +2166,7 @@
         <v>70</v>
       </c>
       <c r="N33" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2218,7 +2218,7 @@
         <v>70</v>
       </c>
       <c r="N34" t="n">
-        <v>450</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="35">
@@ -2250,18 +2250,18 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         <v>70</v>
       </c>
       <c r="N35" t="n">
-        <v>407.7</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36">
@@ -2302,11 +2302,11 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2322,7 +2322,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="n">
-        <v>370</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2374,7 +2374,7 @@
         <v>90</v>
       </c>
       <c r="N37" t="n">
-        <v>530</v>
+        <v>503.3</v>
       </c>
     </row>
     <row r="38">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J38" t="n">
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>3.5</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>410</v>
+        <v>530</v>
       </c>
     </row>
     <row r="39">
@@ -2458,18 +2458,18 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J39" t="n">
         <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>3.5</v>
@@ -2478,7 +2478,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40">
@@ -2510,18 +2510,18 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J40" t="n">
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
         <v>3.5</v>
@@ -2530,7 +2530,7 @@
         <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>670</v>
+        <v>530</v>
       </c>
     </row>
     <row r="41">
@@ -2562,18 +2562,18 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L41" t="n">
         <v>3.5</v>
@@ -2582,7 +2582,7 @@
         <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>660</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42">
@@ -2614,18 +2614,18 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J42" t="n">
         <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L42" t="n">
         <v>3.5</v>
@@ -2634,7 +2634,7 @@
         <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>610</v>
+        <v>660</v>
       </c>
     </row>
     <row r="43">
@@ -2666,18 +2666,18 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L43" t="n">
         <v>3.5</v>
@@ -2686,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>460</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L44" t="n">
         <v>3.5</v>
@@ -2738,7 +2738,7 @@
         <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>660</v>
+        <v>460</v>
       </c>
     </row>
     <row r="45">
@@ -2770,18 +2770,18 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
         <v>3.5</v>
@@ -2790,7 +2790,7 @@
         <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="46">
@@ -2822,18 +2822,18 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L46" t="n">
         <v>3.5</v>
@@ -2842,7 +2842,7 @@
         <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>710</v>
+        <v>610</v>
       </c>
     </row>
     <row r="47">
@@ -2874,18 +2874,18 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J47" t="n">
         <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
         <v>3.5</v>
@@ -2894,7 +2894,7 @@
         <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>520</v>
+        <v>670</v>
       </c>
     </row>
     <row r="48">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2946,7 +2946,7 @@
         <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>590</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49">
@@ -3030,18 +3030,18 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>3.5</v>
@@ -3050,7 +3050,7 @@
         <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>660</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="51">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L51" t="n">
         <v>3.5</v>
@@ -3102,7 +3102,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>457.7</v>
+        <v>670</v>
       </c>
     </row>
     <row r="52">
@@ -3134,18 +3134,18 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3258,7 +3258,7 @@
         <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55">
@@ -3290,11 +3290,11 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3310,7 +3310,7 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="56">
@@ -3342,18 +3342,18 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3362,7 +3362,7 @@
         <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>677.7</v>
+        <v>710</v>
       </c>
     </row>
     <row r="57">
@@ -3446,18 +3446,18 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J58" t="n">
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L58" t="n">
         <v>3.5</v>
@@ -3466,7 +3466,7 @@
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
     </row>
     <row r="59">
@@ -3518,7 +3518,7 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>570</v>
+        <v>630</v>
       </c>
     </row>
     <row r="60">
@@ -3570,7 +3570,7 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>480</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61">
@@ -3602,18 +3602,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L61" t="n">
         <v>4</v>
@@ -3622,7 +3622,7 @@
         <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>740</v>
+        <v>540</v>
       </c>
     </row>
     <row r="62">
@@ -3654,18 +3654,18 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J62" t="n">
         <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L62" t="n">
         <v>4</v>
@@ -3674,7 +3674,7 @@
         <v>50</v>
       </c>
       <c r="N62" t="n">
-        <v>720</v>
+        <v>743.3</v>
       </c>
     </row>
     <row r="63">
@@ -3706,18 +3706,18 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -3726,7 +3726,7 @@
         <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>710</v>
+        <v>780</v>
       </c>
     </row>
     <row r="64">
@@ -3758,18 +3758,18 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -3778,7 +3778,7 @@
         <v>50</v>
       </c>
       <c r="N64" t="n">
-        <v>510</v>
+        <v>750</v>
       </c>
     </row>
     <row r="65">
@@ -3810,18 +3810,18 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L65" t="n">
         <v>4</v>
@@ -3830,7 +3830,7 @@
         <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="66">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3882,7 +3882,7 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="67">
@@ -3914,18 +3914,18 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J67" t="n">
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -3934,7 +3934,7 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="68">
@@ -3966,18 +3966,18 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -3986,7 +3986,7 @@
         <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>780</v>
+        <v>710</v>
       </c>
     </row>
     <row r="69">
@@ -4018,11 +4018,11 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4038,7 +4038,7 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>740</v>
+        <v>770</v>
       </c>
     </row>
     <row r="70">
@@ -4070,11 +4070,11 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4090,7 +4090,7 @@
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>610</v>
+        <v>580</v>
       </c>
     </row>
     <row r="71">
@@ -4142,7 +4142,7 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>740</v>
+        <v>730</v>
       </c>
     </row>
     <row r="72">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4194,7 +4194,7 @@
         <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="73">
@@ -4226,11 +4226,11 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4246,7 +4246,7 @@
         <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="74">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4298,7 +4298,7 @@
         <v>40</v>
       </c>
       <c r="N74" t="n">
-        <v>497.7</v>
+        <v>540</v>
       </c>
     </row>
     <row r="75">
@@ -4330,11 +4330,11 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4350,7 +4350,7 @@
         <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>620</v>
+        <v>573.3</v>
       </c>
     </row>
     <row r="76">
@@ -4434,11 +4434,11 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4454,7 +4454,7 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>530</v>
+        <v>490</v>
       </c>
     </row>
     <row r="78">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4506,7 +4506,7 @@
         <v>80</v>
       </c>
       <c r="N78" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
     </row>
     <row r="79">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4558,7 +4558,7 @@
         <v>80</v>
       </c>
       <c r="N79" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80">
@@ -4590,18 +4590,18 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>670</v>
+        <v>693.3</v>
       </c>
     </row>
     <row r="81">
@@ -4642,18 +4642,18 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J81" t="n">
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4662,7 +4662,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>460</v>
+        <v>730</v>
       </c>
     </row>
     <row r="82">
@@ -4705,7 +4705,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row r="83">
@@ -4757,7 +4757,7 @@
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -4766,7 +4766,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="84">
@@ -4798,18 +4798,18 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J84" t="n">
         <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -4818,7 +4818,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="85">
@@ -4850,18 +4850,18 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4870,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>680</v>
+        <v>530</v>
       </c>
     </row>
     <row r="86">
@@ -4902,18 +4902,18 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>630</v>
+        <v>540</v>
       </c>
     </row>
     <row r="87">
@@ -4954,18 +4954,18 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -4974,7 +4974,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>710</v>
+        <v>553.3</v>
       </c>
     </row>
     <row r="88">
@@ -5006,18 +5006,18 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5026,7 +5026,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>730</v>
+        <v>660</v>
       </c>
     </row>
     <row r="89">
@@ -5058,18 +5058,18 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J89" t="n">
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5078,7 +5078,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>470</v>
+        <v>720</v>
       </c>
     </row>
     <row r="90">
@@ -5110,11 +5110,11 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5130,7 +5130,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
     </row>
     <row r="91">
@@ -5173,7 +5173,7 @@
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L91" t="n">
         <v>5</v>
@@ -5182,7 +5182,7 @@
         <v>70</v>
       </c>
       <c r="N91" t="n">
-        <v>470</v>
+        <v>643.3</v>
       </c>
     </row>
     <row r="92">
@@ -5214,18 +5214,18 @@
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J92" t="n">
         <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>5</v>
@@ -5234,7 +5234,7 @@
         <v>70</v>
       </c>
       <c r="N92" t="n">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93">
@@ -5266,11 +5266,11 @@
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5286,7 +5286,7 @@
         <v>70</v>
       </c>
       <c r="N93" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="94">
@@ -5318,11 +5318,11 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5338,7 +5338,7 @@
         <v>70</v>
       </c>
       <c r="N94" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="95">
@@ -5422,11 +5422,11 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5442,7 +5442,7 @@
         <v>70</v>
       </c>
       <c r="N96" t="n">
-        <v>420</v>
+        <v>330</v>
       </c>
     </row>
     <row r="97">
@@ -5474,18 +5474,18 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L97" t="n">
         <v>5.5</v>
@@ -5494,7 +5494,7 @@
         <v>70</v>
       </c>
       <c r="N97" t="n">
-        <v>420</v>
+        <v>650</v>
       </c>
     </row>
     <row r="98">
@@ -5526,18 +5526,18 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
         <v>5.5</v>
@@ -5546,7 +5546,7 @@
         <v>70</v>
       </c>
       <c r="N98" t="n">
-        <v>610</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99">
@@ -5650,7 +5650,7 @@
         <v>70</v>
       </c>
       <c r="N100" t="n">
-        <v>407.7</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="101">
@@ -5702,7 +5702,7 @@
         <v>70</v>
       </c>
       <c r="N101" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102">
@@ -5745,7 +5745,7 @@
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L102" t="n">
         <v>5.5</v>
@@ -5754,7 +5754,7 @@
         <v>70</v>
       </c>
       <c r="N102" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
     </row>
     <row r="103">
@@ -5797,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L103" t="n">
         <v>5.5</v>
@@ -5806,7 +5806,7 @@
         <v>70</v>
       </c>
       <c r="N103" t="n">
-        <v>530</v>
+        <v>600</v>
       </c>
     </row>
     <row r="104">
@@ -5849,7 +5849,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L104" t="n">
         <v>5.5</v>
@@ -5858,7 +5858,7 @@
         <v>70</v>
       </c>
       <c r="N104" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="105">
@@ -5901,7 +5901,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L105" t="n">
         <v>5.5</v>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -5962,7 +5962,7 @@
         <v>70</v>
       </c>
       <c r="N106" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
     </row>
     <row r="107">
@@ -6014,7 +6014,7 @@
         <v>70</v>
       </c>
       <c r="N107" t="n">
-        <v>430</v>
+        <v>480</v>
       </c>
     </row>
     <row r="108">
@@ -6118,7 +6118,7 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>677.7</v>
+        <v>693.3</v>
       </c>
     </row>
     <row r="110">
@@ -6161,7 +6161,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L110" t="n">
         <v>4</v>
@@ -6170,7 +6170,7 @@
         <v>70</v>
       </c>
       <c r="N110" t="n">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111">
@@ -6222,7 +6222,7 @@
         <v>70</v>
       </c>
       <c r="N111" t="n">
-        <v>530</v>
+        <v>570</v>
       </c>
     </row>
     <row r="112">
@@ -6274,7 +6274,7 @@
         <v>70</v>
       </c>
       <c r="N112" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
     </row>
     <row r="113">
@@ -6326,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="N113" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
     </row>
     <row r="114">
@@ -6410,18 +6410,18 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J115" t="n">
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L115" t="n">
         <v>4</v>
@@ -6430,7 +6430,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>670</v>
+        <v>753.3</v>
       </c>
     </row>
     <row r="116">
@@ -6462,18 +6462,18 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L116" t="n">
         <v>4</v>
@@ -6482,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>540</v>
+        <v>680</v>
       </c>
     </row>
     <row r="117">
@@ -6514,18 +6514,18 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J117" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L117" t="n">
         <v>4</v>
@@ -6534,7 +6534,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="118">
@@ -6577,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
         <v>4</v>
@@ -6586,7 +6586,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>520</v>
+        <v>470</v>
       </c>
     </row>
     <row r="119">
@@ -6618,11 +6618,11 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6638,7 +6638,7 @@
         <v>80</v>
       </c>
       <c r="N119" t="n">
-        <v>560</v>
+        <v>610</v>
       </c>
     </row>
     <row r="120">
@@ -6670,11 +6670,11 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="N120" t="n">
-        <v>577.7</v>
+        <v>620</v>
       </c>
     </row>
     <row r="121">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6742,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="122">
@@ -6826,15 +6826,15 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>90</v>
       </c>
       <c r="N123" t="n">
-        <v>540</v>
+        <v>510</v>
       </c>
     </row>
     <row r="124">
@@ -6878,18 +6878,18 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J124" t="n">
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
@@ -6898,7 +6898,7 @@
         <v>80</v>
       </c>
       <c r="N124" t="n">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="125">
@@ -6930,11 +6930,11 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -6950,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="N125" t="n">
-        <v>660</v>
+        <v>623.3</v>
       </c>
     </row>
     <row r="126">
@@ -6982,11 +6982,11 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7002,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="N126" t="n">
-        <v>660</v>
+        <v>530</v>
       </c>
     </row>
     <row r="127">
@@ -7034,18 +7034,18 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7054,7 +7054,7 @@
         <v>80</v>
       </c>
       <c r="N127" t="n">
-        <v>550</v>
+        <v>633.3</v>
       </c>
     </row>
     <row r="128">
@@ -7086,18 +7086,18 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L128" t="n">
         <v>3</v>
@@ -7106,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="129">
@@ -7138,18 +7138,18 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L129" t="n">
         <v>3</v>
@@ -7158,7 +7158,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="130">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7210,7 +7210,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>450</v>
+        <v>393.3</v>
       </c>
     </row>
     <row r="131">
@@ -7242,11 +7242,11 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -7262,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>790</v>
+        <v>730</v>
       </c>
     </row>
     <row r="132">
@@ -7294,18 +7294,18 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L132" t="n">
         <v>3</v>
@@ -7314,7 +7314,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>387.7</v>
+        <v>410</v>
       </c>
     </row>
     <row r="133">
@@ -7346,18 +7346,18 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7366,7 +7366,7 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>430</v>
+        <v>610</v>
       </c>
     </row>
     <row r="134">
@@ -7398,18 +7398,18 @@
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J134" t="n">
         <v>1</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L134" t="n">
         <v>3</v>
@@ -7418,7 +7418,7 @@
         <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="135">
@@ -7450,18 +7450,18 @@
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J135" t="n">
         <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" t="n">
         <v>4</v>
@@ -7470,7 +7470,7 @@
         <v>80</v>
       </c>
       <c r="N135" t="n">
-        <v>360</v>
+        <v>493.3</v>
       </c>
     </row>
     <row r="136">
@@ -7502,18 +7502,18 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J136" t="n">
         <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>4</v>
@@ -7522,7 +7522,7 @@
         <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>530</v>
+        <v>370</v>
       </c>
     </row>
     <row r="137">
@@ -7554,11 +7554,11 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7574,7 +7574,7 @@
         <v>100</v>
       </c>
       <c r="N137" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="138">
@@ -7658,11 +7658,11 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7678,7 +7678,7 @@
         <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>537.7</v>
+        <v>540</v>
       </c>
     </row>
     <row r="140">
@@ -7710,11 +7710,11 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -7730,7 +7730,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>570</v>
+        <v>610</v>
       </c>
     </row>
     <row r="141">
@@ -7762,18 +7762,18 @@
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J141" t="n">
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -7814,18 +7814,18 @@
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>480</v>
+        <v>580</v>
       </c>
     </row>
     <row r="143">
@@ -7866,18 +7866,18 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J143" t="n">
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -7886,7 +7886,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="144">
@@ -7918,18 +7918,18 @@
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J144" t="n">
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L144" t="n">
         <v>4</v>
@@ -7938,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="N144" t="n">
-        <v>430</v>
+        <v>460</v>
       </c>
     </row>
     <row r="145">
@@ -7970,11 +7970,11 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -7990,7 +7990,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="146">
@@ -8022,18 +8022,18 @@
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8042,7 +8042,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
     </row>
     <row r="147">
@@ -8074,18 +8074,18 @@
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J147" t="n">
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8094,7 +8094,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>580</v>
+        <v>490</v>
       </c>
     </row>
     <row r="148">
@@ -8126,18 +8126,18 @@
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J148" t="n">
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8146,7 +8146,7 @@
         <v>50</v>
       </c>
       <c r="N148" t="n">
-        <v>580</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149">
@@ -8178,18 +8178,18 @@
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J149" t="n">
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8198,7 +8198,7 @@
         <v>50</v>
       </c>
       <c r="N149" t="n">
-        <v>457.7</v>
+        <v>500</v>
       </c>
     </row>
     <row r="150">
@@ -8230,11 +8230,11 @@
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -8250,7 +8250,7 @@
         <v>50</v>
       </c>
       <c r="N150" t="n">
-        <v>570</v>
+        <v>620</v>
       </c>
     </row>
     <row r="151">
@@ -8282,11 +8282,11 @@
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -8302,7 +8302,7 @@
         <v>50</v>
       </c>
       <c r="N151" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
     </row>
     <row r="152">
@@ -8334,18 +8334,18 @@
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J152" t="n">
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L152" t="n">
         <v>4</v>
@@ -8354,7 +8354,7 @@
         <v>70</v>
       </c>
       <c r="N152" t="n">
-        <v>420</v>
+        <v>690</v>
       </c>
     </row>
     <row r="153">
@@ -8386,18 +8386,18 @@
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J153" t="n">
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
         <v>4</v>
@@ -8406,7 +8406,7 @@
         <v>70</v>
       </c>
       <c r="N153" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154">
@@ -8438,18 +8438,18 @@
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J154" t="n">
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L154" t="n">
         <v>4</v>
@@ -8458,7 +8458,7 @@
         <v>70</v>
       </c>
       <c r="N154" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155">
@@ -8490,18 +8490,18 @@
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J155" t="n">
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L155" t="n">
         <v>4</v>
@@ -8510,7 +8510,7 @@
         <v>70</v>
       </c>
       <c r="N155" t="n">
-        <v>457.7</v>
+        <v>410</v>
       </c>
     </row>
     <row r="156">
@@ -8542,18 +8542,18 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J156" t="n">
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L156" t="n">
         <v>4</v>
@@ -8562,7 +8562,7 @@
         <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>380</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="157">
@@ -8594,18 +8594,18 @@
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J157" t="n">
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L157" t="n">
         <v>4</v>
@@ -8614,7 +8614,7 @@
         <v>70</v>
       </c>
       <c r="N157" t="n">
-        <v>750</v>
+        <v>360</v>
       </c>
     </row>
     <row r="158">
@@ -8646,18 +8646,18 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L158" t="n">
         <v>4</v>
@@ -8666,7 +8666,7 @@
         <v>70</v>
       </c>
       <c r="N158" t="n">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="159">
@@ -8698,18 +8698,18 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J159" t="n">
         <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L159" t="n">
         <v>4</v>
@@ -8718,7 +8718,7 @@
         <v>70</v>
       </c>
       <c r="N159" t="n">
-        <v>690</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160">
@@ -8750,11 +8750,11 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8770,7 +8770,7 @@
         <v>80</v>
       </c>
       <c r="N160" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="161">
@@ -8802,11 +8802,11 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -8822,7 +8822,7 @@
         <v>80</v>
       </c>
       <c r="N161" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="162">
@@ -8854,11 +8854,11 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -8874,7 +8874,7 @@
         <v>90</v>
       </c>
       <c r="N162" t="n">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="163">
@@ -8917,7 +8917,7 @@
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -8926,7 +8926,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>530</v>
+        <v>580</v>
       </c>
     </row>
     <row r="164">
@@ -8958,18 +8958,18 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
     </row>
     <row r="165">
@@ -9010,18 +9010,18 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>530</v>
+        <v>700</v>
       </c>
     </row>
     <row r="166">
@@ -9073,7 +9073,7 @@
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9082,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>410</v>
+        <v>450</v>
       </c>
     </row>
     <row r="167">
@@ -9134,7 +9134,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
     </row>
     <row r="168">
@@ -9166,18 +9166,18 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9186,7 +9186,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="169">
@@ -9218,18 +9218,18 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9238,7 +9238,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>450</v>
+        <v>660</v>
       </c>
     </row>
     <row r="170">
@@ -9270,11 +9270,11 @@
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9290,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>627.7</v>
+        <v>670</v>
       </c>
     </row>
     <row r="171">
@@ -9322,18 +9322,18 @@
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J171" t="n">
         <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L171" t="n">
         <v>3</v>
@@ -9342,7 +9342,7 @@
         <v>50</v>
       </c>
       <c r="N171" t="n">
-        <v>600</v>
+        <v>683.3</v>
       </c>
     </row>
     <row r="172">
@@ -9374,18 +9374,18 @@
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
@@ -9394,7 +9394,7 @@
         <v>50</v>
       </c>
       <c r="N172" t="n">
-        <v>690</v>
+        <v>530</v>
       </c>
     </row>
     <row r="173">
@@ -9437,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="K173" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L173" t="n">
         <v>3</v>
@@ -9446,7 +9446,7 @@
         <v>50</v>
       </c>
       <c r="N173" t="n">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="174">
@@ -9478,11 +9478,11 @@
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9498,7 +9498,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>540</v>
+        <v>543.3</v>
       </c>
     </row>
     <row r="175">
@@ -9530,11 +9530,11 @@
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9550,7 +9550,7 @@
         <v>80</v>
       </c>
       <c r="N175" t="n">
-        <v>610</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -9782,7 +9782,9 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
@@ -9790,9 +9792,7 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
@@ -9825,9 +9825,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>1</v>
@@ -9841,7 +9839,9 @@
       <c r="Z4" t="n">
         <v>1</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
@@ -9854,38 +9854,36 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -10011,28 +10009,30 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
@@ -10050,17 +10050,13 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -10089,21 +10085,25 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
@@ -10113,9 +10113,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>1</v>
@@ -10124,10 +10122,10 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -10153,7 +10151,9 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -10185,9 +10185,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10196,9 +10194,7 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -10208,18 +10204,18 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -10234,7 +10230,9 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10243,7 +10241,9 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -10266,9 +10266,7 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -10333,40 +10331,40 @@
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -10423,36 +10421,38 @@
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -10516,9 +10516,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>1</v>
@@ -10527,34 +10525,36 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -10562,15 +10562,15 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>1</v>
@@ -10580,10 +10580,10 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -10643,20 +10643,18 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -10671,7 +10669,9 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -10718,14 +10718,14 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -10791,7 +10791,9 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
@@ -10800,9 +10802,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
@@ -10812,23 +10812,21 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
@@ -10846,10 +10844,10 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -10867,15 +10865,15 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -10892,10 +10890,10 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -10932,11 +10930,11 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -10977,30 +10975,28 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
         <v>1</v>
       </c>
@@ -11008,20 +11004,20 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -11040,7 +11036,9 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
@@ -11061,28 +11059,28 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="n">
@@ -11092,10 +11090,10 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
@@ -11111,25 +11109,27 @@
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
@@ -11139,17 +11139,15 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11193,28 +11191,30 @@
       <c r="B36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -11229,9 +11229,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -11240,16 +11238,18 @@
       <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>1</v>
@@ -11258,10 +11258,10 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -11269,10 +11269,10 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
@@ -11285,9 +11285,7 @@
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -11321,33 +11319,35 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -11358,9 +11358,7 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
@@ -11368,7 +11366,9 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -11377,37 +11377,37 @@
       <c r="B40" t="n">
         <v>1</v>
       </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
@@ -11436,13 +11436,11 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
         <v>1</v>
       </c>
@@ -11450,7 +11448,9 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="n">
         <v>1</v>
@@ -11464,12 +11464,12 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -11486,20 +11486,20 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>

--- a/Data/04_26_schedule_results.xlsx
+++ b/Data/04_26_schedule_results.xlsx
@@ -538,11 +538,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -558,7 +558,7 @@
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -614,7 +614,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>490</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4">
@@ -650,18 +650,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>3.5</v>
@@ -670,7 +670,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>470</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5">
@@ -706,18 +706,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>3.5</v>
@@ -726,7 +726,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>683.3</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6">
@@ -762,18 +762,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>3.5</v>
@@ -782,7 +782,7 @@
         <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>690</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7">
@@ -818,18 +818,18 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>3.5</v>
@@ -838,7 +838,7 @@
         <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>460</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8">
@@ -874,18 +874,18 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
         <v>3.5</v>
@@ -894,7 +894,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>770</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9">
@@ -930,18 +930,18 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>3.5</v>
@@ -950,7 +950,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10">
@@ -986,18 +986,18 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
         <v>3.5</v>
@@ -1006,7 +1006,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>413.3</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11">
@@ -1042,18 +1042,18 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
         <v>3.5</v>
@@ -1062,7 +1062,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12">
@@ -1098,18 +1098,18 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>3.5</v>
@@ -1118,7 +1118,7 @@
         <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>400</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="13">
@@ -1154,18 +1154,18 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>3.5</v>
@@ -1174,7 +1174,7 @@
         <v>70</v>
       </c>
       <c r="N13" t="n">
-        <v>690</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14">
@@ -1210,18 +1210,18 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1230,7 +1230,7 @@
         <v>70</v>
       </c>
       <c r="N14" t="n">
-        <v>683.3</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15">
@@ -1266,18 +1266,18 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>3.5</v>
@@ -1286,7 +1286,7 @@
         <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>670</v>
+        <v>580</v>
       </c>
     </row>
     <row r="16">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1342,7 +1342,7 @@
         <v>70</v>
       </c>
       <c r="N16" t="n">
-        <v>540</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17">
@@ -1378,11 +1378,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1398,7 +1398,7 @@
         <v>80</v>
       </c>
       <c r="N17" t="n">
-        <v>690</v>
+        <v>620</v>
       </c>
     </row>
     <row r="18">
@@ -1434,18 +1434,18 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1454,7 +1454,7 @@
         <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>690</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19">
@@ -1490,18 +1490,18 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1510,7 +1510,7 @@
         <v>70</v>
       </c>
       <c r="N19" t="n">
-        <v>660</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20">
@@ -1546,18 +1546,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1566,7 +1566,7 @@
         <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>470</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21">
@@ -1602,18 +1602,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1622,7 +1622,7 @@
         <v>70</v>
       </c>
       <c r="N21" t="n">
-        <v>490</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22">
@@ -1658,18 +1658,18 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1678,7 +1678,7 @@
         <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23">
@@ -1714,18 +1714,18 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1734,7 +1734,7 @@
         <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>670</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24">
@@ -1770,18 +1770,18 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1790,7 +1790,7 @@
         <v>70</v>
       </c>
       <c r="N24" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25">
@@ -1826,18 +1826,18 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Margrét Lára</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1846,7 +1846,7 @@
         <v>70</v>
       </c>
       <c r="N25" t="n">
-        <v>483.3</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26">
@@ -1882,18 +1882,18 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1902,7 +1902,7 @@
         <v>70</v>
       </c>
       <c r="N26" t="n">
-        <v>410</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27">
@@ -1938,18 +1938,18 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>3</v>
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="N27" t="n">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28">
@@ -1994,18 +1994,18 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -2014,7 +2014,7 @@
         <v>70</v>
       </c>
       <c r="N28" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29">
@@ -2050,18 +2050,18 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J29" t="n">
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>3</v>
@@ -2070,7 +2070,7 @@
         <v>70</v>
       </c>
       <c r="N29" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="30">
@@ -2106,18 +2106,18 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2126,7 +2126,7 @@
         <v>70</v>
       </c>
       <c r="N30" t="n">
-        <v>570</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31">
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2182,7 +2182,7 @@
         <v>70</v>
       </c>
       <c r="N31" t="n">
-        <v>400</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="32">
@@ -2218,18 +2218,18 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2238,7 +2238,7 @@
         <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>573.3</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33">
@@ -2274,11 +2274,11 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2294,7 +2294,7 @@
         <v>70</v>
       </c>
       <c r="N33" t="n">
-        <v>410</v>
+        <v>480</v>
       </c>
     </row>
     <row r="34">
@@ -2330,18 +2330,18 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Margrét Lára</t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2350,7 +2350,7 @@
         <v>70</v>
       </c>
       <c r="N34" t="n">
-        <v>400</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="35">
@@ -2386,18 +2386,18 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2406,7 +2406,7 @@
         <v>70</v>
       </c>
       <c r="N35" t="n">
-        <v>360</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36">
@@ -2442,11 +2442,11 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2462,7 +2462,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37">
@@ -2498,11 +2498,11 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2554,18 +2554,18 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J38" t="n">
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
         <v>3.5</v>
@@ -2574,7 +2574,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39">
@@ -2621,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>3.5</v>
@@ -2630,7 +2630,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>690</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40">
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
         <v>3.5</v>
@@ -2686,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>630</v>
+        <v>530</v>
       </c>
     </row>
     <row r="41">
@@ -2722,18 +2722,18 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L41" t="n">
         <v>3.5</v>
@@ -2742,7 +2742,7 @@
         <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42">
@@ -2778,18 +2778,18 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J42" t="n">
         <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L42" t="n">
         <v>3.5</v>
@@ -2798,7 +2798,7 @@
         <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>610</v>
+        <v>660</v>
       </c>
     </row>
     <row r="43">
@@ -2834,18 +2834,18 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L43" t="n">
         <v>3.5</v>
@@ -2854,7 +2854,7 @@
         <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>540</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44">
@@ -2890,18 +2890,18 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>3.5</v>
@@ -2910,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>720</v>
+        <v>530</v>
       </c>
     </row>
     <row r="45">
@@ -2946,18 +2946,18 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L45" t="n">
         <v>3.5</v>
@@ -3002,18 +3002,18 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
         <v>3.5</v>
@@ -3022,7 +3022,7 @@
         <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>720</v>
+        <v>610</v>
       </c>
     </row>
     <row r="47">
@@ -3058,18 +3058,18 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L47" t="n">
         <v>3.5</v>
@@ -3078,7 +3078,7 @@
         <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48">
@@ -3114,18 +3114,18 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J48" t="n">
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>3.5</v>
@@ -3134,7 +3134,7 @@
         <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>690</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49">
@@ -3170,18 +3170,18 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J49" t="n">
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
         <v>3.5</v>
@@ -3190,7 +3190,7 @@
         <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>410</v>
+        <v>660</v>
       </c>
     </row>
     <row r="50">
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3246,7 +3246,7 @@
         <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="51">
@@ -3282,18 +3282,18 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>3.5</v>
@@ -3302,7 +3302,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>620</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="52">
@@ -3338,18 +3338,18 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3358,7 +3358,7 @@
         <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>600</v>
+        <v>670</v>
       </c>
     </row>
     <row r="53">
@@ -3394,18 +3394,18 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L53" t="n">
         <v>3.5</v>
@@ -3414,7 +3414,7 @@
         <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>410</v>
+        <v>710</v>
       </c>
     </row>
     <row r="54">
@@ -3450,18 +3450,18 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L54" t="n">
         <v>3.5</v>
@@ -3470,7 +3470,7 @@
         <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
     </row>
     <row r="55">
@@ -3506,18 +3506,18 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3526,7 +3526,7 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>590</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56">
@@ -3562,18 +3562,18 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3582,7 +3582,7 @@
         <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>540</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57">
@@ -3618,18 +3618,18 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>3.5</v>
@@ -3638,7 +3638,7 @@
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="58">
@@ -3685,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>3.5</v>
@@ -3694,7 +3694,7 @@
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="59">
@@ -3750,7 +3750,7 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>470</v>
+        <v>630</v>
       </c>
     </row>
     <row r="60">
@@ -3786,18 +3786,18 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J60" t="n">
         <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L60" t="n">
         <v>4</v>
@@ -3806,7 +3806,7 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>590</v>
+        <v>480</v>
       </c>
     </row>
     <row r="61">
@@ -3842,18 +3842,18 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L61" t="n">
         <v>4</v>
@@ -3862,7 +3862,7 @@
         <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>463.3</v>
+        <v>540</v>
       </c>
     </row>
     <row r="62">
@@ -3898,18 +3898,18 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J62" t="n">
         <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L62" t="n">
         <v>4</v>
@@ -3918,7 +3918,7 @@
         <v>50</v>
       </c>
       <c r="N62" t="n">
-        <v>693.3</v>
+        <v>730</v>
       </c>
     </row>
     <row r="63">
@@ -3965,7 +3965,7 @@
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -3974,7 +3974,7 @@
         <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="64">
@@ -4010,18 +4010,18 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -4030,7 +4030,7 @@
         <v>50</v>
       </c>
       <c r="N64" t="n">
-        <v>420</v>
+        <v>750</v>
       </c>
     </row>
     <row r="65">
@@ -4066,18 +4066,18 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L65" t="n">
         <v>4</v>
@@ -4086,7 +4086,7 @@
         <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>630</v>
+        <v>750</v>
       </c>
     </row>
     <row r="66">
@@ -4122,18 +4122,18 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>4</v>
@@ -4142,7 +4142,7 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>640</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67">
@@ -4178,18 +4178,18 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J67" t="n">
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -4198,7 +4198,7 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>463.3</v>
+        <v>720</v>
       </c>
     </row>
     <row r="68">
@@ -4234,18 +4234,18 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -4290,18 +4290,18 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J69" t="n">
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -4310,7 +4310,7 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>670</v>
+        <v>780</v>
       </c>
     </row>
     <row r="70">
@@ -4366,7 +4366,7 @@
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
     </row>
     <row r="71">
@@ -4402,18 +4402,18 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J71" t="n">
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4422,7 +4422,7 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>610</v>
+        <v>730</v>
       </c>
     </row>
     <row r="72">
@@ -4458,11 +4458,11 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4514,11 +4514,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4534,7 +4534,7 @@
         <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>390</v>
+        <v>490</v>
       </c>
     </row>
     <row r="74">
@@ -4570,11 +4570,11 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4590,7 +4590,7 @@
         <v>40</v>
       </c>
       <c r="N74" t="n">
-        <v>470</v>
+        <v>560</v>
       </c>
     </row>
     <row r="75">
@@ -4626,11 +4626,11 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4646,7 +4646,7 @@
         <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>480</v>
+        <v>573.3</v>
       </c>
     </row>
     <row r="76">
@@ -4682,11 +4682,11 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4702,7 +4702,7 @@
         <v>40</v>
       </c>
       <c r="N76" t="n">
-        <v>490</v>
+        <v>460</v>
       </c>
     </row>
     <row r="77">
@@ -4738,11 +4738,11 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4758,7 +4758,7 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="78">
@@ -4794,15 +4794,15 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
@@ -4814,7 +4814,7 @@
         <v>80</v>
       </c>
       <c r="N78" t="n">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row r="79">
@@ -4850,11 +4850,11 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4870,7 +4870,7 @@
         <v>80</v>
       </c>
       <c r="N79" t="n">
-        <v>510</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80">
@@ -4906,18 +4906,18 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4926,7 +4926,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>540</v>
+        <v>693.3</v>
       </c>
     </row>
     <row r="81">
@@ -4962,18 +4962,18 @@
         </is>
       </c>
       <c r="H81" t="n">
+        <v>10</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erna </t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" t="n">
         <v>5</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auður </t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>2</v>
-      </c>
-      <c r="K81" t="n">
-        <v>4</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4982,7 +4982,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="82">
@@ -5018,18 +5018,18 @@
         </is>
       </c>
       <c r="H82" t="n">
+        <v>12</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Gréta</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="n">
         <v>8</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elísabet </t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" t="n">
-        <v>9</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -5038,7 +5038,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>733.3</v>
+        <v>730</v>
       </c>
     </row>
     <row r="83">
@@ -5074,18 +5074,18 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -5094,7 +5094,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>790</v>
+        <v>620</v>
       </c>
     </row>
     <row r="84">
@@ -5130,18 +5130,18 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J84" t="n">
         <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -5150,7 +5150,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>550</v>
+        <v>740</v>
       </c>
     </row>
     <row r="85">
@@ -5186,18 +5186,18 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -5242,18 +5242,18 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -5262,7 +5262,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>440</v>
+        <v>540</v>
       </c>
     </row>
     <row r="87">
@@ -5298,18 +5298,18 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -5318,7 +5318,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>740</v>
+        <v>553.3</v>
       </c>
     </row>
     <row r="88">
@@ -5354,18 +5354,18 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J88" t="n">
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5374,7 +5374,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>733.3</v>
+        <v>550</v>
       </c>
     </row>
     <row r="89">
@@ -5421,7 +5421,7 @@
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5430,7 +5430,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>780</v>
+        <v>730</v>
       </c>
     </row>
     <row r="90">
@@ -5466,11 +5466,11 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5486,7 +5486,7 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>430</v>
+        <v>560</v>
       </c>
     </row>
     <row r="91">
@@ -5533,7 +5533,7 @@
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L91" t="n">
         <v>5</v>
@@ -5542,7 +5542,7 @@
         <v>70</v>
       </c>
       <c r="N91" t="n">
-        <v>413.3</v>
+        <v>643.3</v>
       </c>
     </row>
     <row r="92">
@@ -5578,18 +5578,18 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J92" t="n">
         <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>5</v>
@@ -5598,7 +5598,7 @@
         <v>70</v>
       </c>
       <c r="N92" t="n">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93">
@@ -5634,18 +5634,18 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J93" t="n">
         <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
         <v>5</v>
@@ -5654,7 +5654,7 @@
         <v>70</v>
       </c>
       <c r="N93" t="n">
-        <v>430</v>
+        <v>480</v>
       </c>
     </row>
     <row r="94">
@@ -5690,18 +5690,18 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J94" t="n">
         <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
         <v>5</v>
@@ -5710,7 +5710,7 @@
         <v>70</v>
       </c>
       <c r="N94" t="n">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="95">
@@ -5746,18 +5746,18 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J95" t="n">
         <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L95" t="n">
         <v>5</v>
@@ -5766,7 +5766,7 @@
         <v>70</v>
       </c>
       <c r="N95" t="n">
-        <v>413.3</v>
+        <v>390</v>
       </c>
     </row>
     <row r="96">
@@ -5802,11 +5802,11 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5822,7 +5822,7 @@
         <v>70</v>
       </c>
       <c r="N96" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
     </row>
     <row r="97">
@@ -5858,18 +5858,18 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J97" t="n">
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L97" t="n">
         <v>5.5</v>
@@ -5878,7 +5878,7 @@
         <v>70</v>
       </c>
       <c r="N97" t="n">
-        <v>470</v>
+        <v>600</v>
       </c>
     </row>
     <row r="98">
@@ -5914,18 +5914,18 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L98" t="n">
         <v>5.5</v>
@@ -5934,7 +5934,7 @@
         <v>70</v>
       </c>
       <c r="N98" t="n">
-        <v>480</v>
+        <v>410</v>
       </c>
     </row>
     <row r="99">
@@ -5970,18 +5970,18 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J99" t="n">
         <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L99" t="n">
         <v>5.5</v>
@@ -5990,7 +5990,7 @@
         <v>70</v>
       </c>
       <c r="N99" t="n">
-        <v>700</v>
+        <v>530</v>
       </c>
     </row>
     <row r="100">
@@ -6026,18 +6026,18 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J100" t="n">
         <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>5.5</v>
@@ -6046,7 +6046,7 @@
         <v>70</v>
       </c>
       <c r="N100" t="n">
-        <v>580</v>
+        <v>413.3</v>
       </c>
     </row>
     <row r="101">
@@ -6082,18 +6082,18 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J101" t="n">
         <v>2</v>
       </c>
       <c r="K101" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L101" t="n">
         <v>5.5</v>
@@ -6102,7 +6102,7 @@
         <v>70</v>
       </c>
       <c r="N101" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="102">
@@ -6138,18 +6138,18 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L102" t="n">
         <v>5.5</v>
@@ -6158,7 +6158,7 @@
         <v>70</v>
       </c>
       <c r="N102" t="n">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row r="103">
@@ -6194,18 +6194,18 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L103" t="n">
         <v>5.5</v>
@@ -6214,7 +6214,7 @@
         <v>70</v>
       </c>
       <c r="N103" t="n">
-        <v>650</v>
+        <v>410</v>
       </c>
     </row>
     <row r="104">
@@ -6250,18 +6250,18 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J104" t="n">
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L104" t="n">
         <v>5.5</v>
@@ -6270,7 +6270,7 @@
         <v>70</v>
       </c>
       <c r="N104" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="105">
@@ -6306,18 +6306,18 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J105" t="n">
         <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L105" t="n">
         <v>5.5</v>
@@ -6326,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="N105" t="n">
-        <v>470</v>
+        <v>520</v>
       </c>
     </row>
     <row r="106">
@@ -6382,7 +6382,7 @@
         <v>70</v>
       </c>
       <c r="N106" t="n">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row r="107">
@@ -6418,18 +6418,18 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Alda/ Miðó </t>
         </is>
       </c>
       <c r="J107" t="n">
         <v>2</v>
       </c>
       <c r="K107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L107" t="n">
         <v>4</v>
@@ -6438,7 +6438,7 @@
         <v>70</v>
       </c>
       <c r="N107" t="n">
-        <v>613.3</v>
+        <v>430</v>
       </c>
     </row>
     <row r="108">
@@ -6474,18 +6474,18 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J108" t="n">
         <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L108" t="n">
         <v>4</v>
@@ -6494,7 +6494,7 @@
         <v>70</v>
       </c>
       <c r="N108" t="n">
-        <v>643.3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="109">
@@ -6530,18 +6530,18 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J109" t="n">
         <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L109" t="n">
         <v>4</v>
@@ -6550,7 +6550,7 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>480</v>
+        <v>693.3</v>
       </c>
     </row>
     <row r="110">
@@ -6597,7 +6597,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L110" t="n">
         <v>4</v>
@@ -6606,7 +6606,7 @@
         <v>70</v>
       </c>
       <c r="N110" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="111">
@@ -6642,18 +6642,18 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>4</v>
@@ -6662,7 +6662,7 @@
         <v>70</v>
       </c>
       <c r="N111" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
     </row>
     <row r="112">
@@ -6698,18 +6698,18 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L112" t="n">
         <v>4</v>
@@ -6718,7 +6718,7 @@
         <v>70</v>
       </c>
       <c r="N112" t="n">
-        <v>480</v>
+        <v>430</v>
       </c>
     </row>
     <row r="113">
@@ -6754,18 +6754,18 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J113" t="n">
         <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L113" t="n">
         <v>4</v>
@@ -6774,7 +6774,7 @@
         <v>70</v>
       </c>
       <c r="N113" t="n">
-        <v>570</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114">
@@ -6810,18 +6810,18 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J114" t="n">
         <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L114" t="n">
         <v>4</v>
@@ -6830,7 +6830,7 @@
         <v>70</v>
       </c>
       <c r="N114" t="n">
-        <v>470</v>
+        <v>753.3</v>
       </c>
     </row>
     <row r="115">
@@ -6866,18 +6866,18 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J115" t="n">
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L115" t="n">
         <v>4</v>
@@ -6886,7 +6886,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="116">
@@ -6922,18 +6922,18 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L116" t="n">
         <v>4</v>
@@ -6942,7 +6942,7 @@
         <v>70</v>
       </c>
       <c r="N116" t="n">
-        <v>613.3</v>
+        <v>650</v>
       </c>
     </row>
     <row r="117">
@@ -6978,18 +6978,18 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L117" t="n">
         <v>4</v>
@@ -6998,7 +6998,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>390</v>
+        <v>680</v>
       </c>
     </row>
     <row r="118">
@@ -7054,7 +7054,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>330</v>
+        <v>470</v>
       </c>
     </row>
     <row r="119">
@@ -7090,11 +7090,11 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -7110,7 +7110,7 @@
         <v>80</v>
       </c>
       <c r="N119" t="n">
-        <v>490</v>
+        <v>620</v>
       </c>
     </row>
     <row r="120">
@@ -7146,11 +7146,11 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -7166,7 +7166,7 @@
         <v>80</v>
       </c>
       <c r="N120" t="n">
-        <v>490</v>
+        <v>630</v>
       </c>
     </row>
     <row r="121">
@@ -7202,11 +7202,11 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -7222,7 +7222,7 @@
         <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>670</v>
+        <v>570</v>
       </c>
     </row>
     <row r="122">
@@ -7258,11 +7258,11 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -7278,7 +7278,7 @@
         <v>40</v>
       </c>
       <c r="N122" t="n">
-        <v>580</v>
+        <v>430</v>
       </c>
     </row>
     <row r="123">
@@ -7314,15 +7314,15 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -7334,7 +7334,7 @@
         <v>90</v>
       </c>
       <c r="N123" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="124">
@@ -7370,18 +7370,18 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J124" t="n">
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
@@ -7390,7 +7390,7 @@
         <v>80</v>
       </c>
       <c r="N124" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="125">
@@ -7426,18 +7426,18 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J125" t="n">
         <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" t="n">
         <v>3</v>
@@ -7446,7 +7446,7 @@
         <v>80</v>
       </c>
       <c r="N125" t="n">
-        <v>550</v>
+        <v>623.3</v>
       </c>
     </row>
     <row r="126">
@@ -7482,18 +7482,18 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J126" t="n">
         <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L126" t="n">
         <v>3</v>
@@ -7502,7 +7502,7 @@
         <v>80</v>
       </c>
       <c r="N126" t="n">
-        <v>600</v>
+        <v>530</v>
       </c>
     </row>
     <row r="127">
@@ -7538,18 +7538,18 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7558,7 +7558,7 @@
         <v>80</v>
       </c>
       <c r="N127" t="n">
-        <v>570</v>
+        <v>633.3</v>
       </c>
     </row>
     <row r="128">
@@ -7594,18 +7594,18 @@
         </is>
       </c>
       <c r="H128" t="n">
+        <v>11</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gaukur </t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>2</v>
+      </c>
+      <c r="K128" t="n">
         <v>5</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auður </t>
-        </is>
-      </c>
-      <c r="J128" t="n">
-        <v>2</v>
-      </c>
-      <c r="K128" t="n">
-        <v>1</v>
       </c>
       <c r="L128" t="n">
         <v>3</v>
@@ -7614,7 +7614,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>400</v>
+        <v>590</v>
       </c>
     </row>
     <row r="129">
@@ -7650,18 +7650,18 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L129" t="n">
         <v>3</v>
@@ -7670,7 +7670,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="130">
@@ -7706,18 +7706,18 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7726,7 +7726,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>390</v>
+        <v>393.3</v>
       </c>
     </row>
     <row r="131">
@@ -7762,18 +7762,18 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J131" t="n">
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L131" t="n">
         <v>3</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>443.3</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132">
@@ -7818,18 +7818,18 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L132" t="n">
         <v>3</v>
@@ -7838,7 +7838,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>340</v>
+        <v>740</v>
       </c>
     </row>
     <row r="133">
@@ -7874,11 +7874,11 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7894,7 +7894,7 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>380</v>
+        <v>610</v>
       </c>
     </row>
     <row r="134">
@@ -7930,18 +7930,18 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J134" t="n">
         <v>1</v>
       </c>
       <c r="K134" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L134" t="n">
         <v>3</v>
@@ -7950,7 +7950,7 @@
         <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="135">
@@ -7986,18 +7986,18 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J135" t="n">
         <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" t="n">
         <v>4</v>
@@ -8006,7 +8006,7 @@
         <v>80</v>
       </c>
       <c r="N135" t="n">
-        <v>370</v>
+        <v>493.3</v>
       </c>
     </row>
     <row r="136">
@@ -8042,18 +8042,18 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J136" t="n">
         <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>4</v>
@@ -8062,7 +8062,7 @@
         <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>560</v>
+        <v>370</v>
       </c>
     </row>
     <row r="137">
@@ -8098,15 +8098,15 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
         <v>100</v>
       </c>
       <c r="N137" t="n">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="138">
@@ -8154,11 +8154,11 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -8174,7 +8174,7 @@
         <v>80</v>
       </c>
       <c r="N138" t="n">
-        <v>543.3</v>
+        <v>540</v>
       </c>
     </row>
     <row r="139">
@@ -8210,11 +8210,11 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -8230,7 +8230,7 @@
         <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>543.3</v>
+        <v>540</v>
       </c>
     </row>
     <row r="140">
@@ -8266,18 +8266,18 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J140" t="n">
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -8286,7 +8286,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141">
@@ -8322,18 +8322,18 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J141" t="n">
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -8342,7 +8342,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>520</v>
+        <v>470</v>
       </c>
     </row>
     <row r="142">
@@ -8378,18 +8378,18 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -8398,7 +8398,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>400</v>
+        <v>630</v>
       </c>
     </row>
     <row r="143">
@@ -8434,18 +8434,18 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J143" t="n">
         <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L143" t="n">
         <v>4</v>
@@ -8454,7 +8454,7 @@
         <v>50</v>
       </c>
       <c r="N143" t="n">
-        <v>530</v>
+        <v>580</v>
       </c>
     </row>
     <row r="144">
@@ -8546,18 +8546,18 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J145" t="n">
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -8566,7 +8566,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>393.3</v>
+        <v>450</v>
       </c>
     </row>
     <row r="146">
@@ -8602,18 +8602,18 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8622,7 +8622,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
     </row>
     <row r="147">
@@ -8669,7 +8669,7 @@
         <v>2</v>
       </c>
       <c r="K147" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
         <v>4</v>
@@ -8725,7 +8725,7 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8781,7 +8781,7 @@
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8837,7 +8837,7 @@
         <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L150" t="n">
         <v>4</v>
@@ -8846,7 +8846,7 @@
         <v>50</v>
       </c>
       <c r="N150" t="n">
-        <v>520</v>
+        <v>610</v>
       </c>
     </row>
     <row r="151">
@@ -8902,7 +8902,7 @@
         <v>50</v>
       </c>
       <c r="N151" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="152">
@@ -8938,18 +8938,18 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alda/ Miðó </t>
+          <t xml:space="preserve">Auður </t>
         </is>
       </c>
       <c r="J152" t="n">
         <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L152" t="n">
         <v>4</v>
@@ -8958,7 +8958,7 @@
         <v>70</v>
       </c>
       <c r="N152" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153">
@@ -8994,18 +8994,18 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J153" t="n">
         <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L153" t="n">
         <v>4</v>
@@ -9014,7 +9014,7 @@
         <v>70</v>
       </c>
       <c r="N153" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154">
@@ -9050,18 +9050,18 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auður </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J154" t="n">
         <v>2</v>
       </c>
       <c r="K154" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L154" t="n">
         <v>4</v>
@@ -9070,7 +9070,7 @@
         <v>70</v>
       </c>
       <c r="N154" t="n">
-        <v>540</v>
+        <v>410</v>
       </c>
     </row>
     <row r="155">
@@ -9106,18 +9106,18 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J155" t="n">
         <v>2</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L155" t="n">
         <v>4</v>
@@ -9126,7 +9126,7 @@
         <v>70</v>
       </c>
       <c r="N155" t="n">
-        <v>413.3</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="156">
@@ -9162,18 +9162,18 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J156" t="n">
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L156" t="n">
         <v>4</v>
@@ -9182,7 +9182,7 @@
         <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>400</v>
+        <v>690</v>
       </c>
     </row>
     <row r="157">
@@ -9218,11 +9218,11 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -9238,7 +9238,7 @@
         <v>70</v>
       </c>
       <c r="N157" t="n">
-        <v>410</v>
+        <v>360</v>
       </c>
     </row>
     <row r="158">
@@ -9274,18 +9274,18 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J158" t="n">
         <v>2</v>
       </c>
       <c r="K158" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L158" t="n">
         <v>4</v>
@@ -9294,7 +9294,7 @@
         <v>70</v>
       </c>
       <c r="N158" t="n">
-        <v>510</v>
+        <v>620</v>
       </c>
     </row>
     <row r="159">
@@ -9330,11 +9330,11 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -9350,7 +9350,7 @@
         <v>70</v>
       </c>
       <c r="N159" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160">
@@ -9386,18 +9386,18 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J160" t="n">
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
@@ -9442,18 +9442,18 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J161" t="n">
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>3</v>
@@ -9462,7 +9462,7 @@
         <v>80</v>
       </c>
       <c r="N161" t="n">
-        <v>490</v>
+        <v>530</v>
       </c>
     </row>
     <row r="162">
@@ -9498,11 +9498,11 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -9518,7 +9518,7 @@
         <v>90</v>
       </c>
       <c r="N162" t="n">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="163">
@@ -9565,7 +9565,7 @@
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -9574,7 +9574,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>610</v>
+        <v>530</v>
       </c>
     </row>
     <row r="164">
@@ -9610,18 +9610,18 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -9630,7 +9630,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>570</v>
+        <v>460</v>
       </c>
     </row>
     <row r="165">
@@ -9666,18 +9666,18 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9686,7 +9686,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>570</v>
+        <v>670</v>
       </c>
     </row>
     <row r="166">
@@ -9722,18 +9722,18 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J166" t="n">
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9742,7 +9742,7 @@
         <v>50</v>
       </c>
       <c r="N166" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="167">
@@ -9778,18 +9778,18 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J167" t="n">
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9798,7 +9798,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>560</v>
+        <v>450</v>
       </c>
     </row>
     <row r="168">
@@ -9834,18 +9834,18 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9854,7 +9854,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="169">
@@ -9890,18 +9890,18 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9910,7 +9910,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="170">
@@ -9946,18 +9946,18 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J170" t="n">
         <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L170" t="n">
         <v>3</v>
@@ -9966,7 +9966,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row r="171">
@@ -10002,18 +10002,18 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L171" t="n">
         <v>3</v>
@@ -10022,7 +10022,7 @@
         <v>50</v>
       </c>
       <c r="N171" t="n">
-        <v>650</v>
+        <v>683.3</v>
       </c>
     </row>
     <row r="172">
@@ -10058,18 +10058,18 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J172" t="n">
         <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
@@ -10078,7 +10078,7 @@
         <v>50</v>
       </c>
       <c r="N172" t="n">
-        <v>660</v>
+        <v>530</v>
       </c>
     </row>
     <row r="173">
@@ -10125,7 +10125,7 @@
         <v>1</v>
       </c>
       <c r="K173" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L173" t="n">
         <v>3</v>
@@ -10134,7 +10134,7 @@
         <v>50</v>
       </c>
       <c r="N173" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="174">
@@ -10170,11 +10170,11 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -10190,7 +10190,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>640</v>
+        <v>543.3</v>
       </c>
     </row>
     <row r="175">
@@ -10226,11 +10226,11 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -10246,7 +10246,7 @@
         <v>80</v>
       </c>
       <c r="N175" t="n">
-        <v>620</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -10468,17 +10468,19 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
@@ -10488,9 +10490,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -10502,14 +10502,12 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -10522,35 +10520,35 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>1</v>
@@ -10560,19 +10558,19 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -10580,23 +10578,23 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -10609,21 +10607,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>1</v>
@@ -10707,22 +10707,22 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -10733,9 +10733,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -10757,27 +10755,25 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
@@ -10785,15 +10781,17 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
       <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10802,29 +10800,31 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -10838,20 +10838,18 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -10877,29 +10875,33 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>1</v>
@@ -10912,17 +10914,13 @@
         <v>1</v>
       </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
@@ -10936,7 +10934,9 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
@@ -10949,18 +10949,18 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -10975,17 +10975,13 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>1</v>
       </c>
@@ -11004,7 +11000,9 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -11014,12 +11012,12 @@
         <v>1</v>
       </c>
       <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -11040,19 +11038,19 @@
         <v>1</v>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -11065,7 +11063,9 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11079,18 +11079,20 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
@@ -11100,9 +11102,7 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
@@ -11114,12 +11114,14 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -11127,19 +11129,17 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -11152,7 +11152,9 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -11185,10 +11187,10 @@
       <c r="Y19" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
@@ -11198,42 +11200,42 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
@@ -11243,10 +11245,10 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -11262,27 +11264,27 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11323,34 +11325,32 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -11363,21 +11363,21 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -11419,9 +11419,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -11440,12 +11438,12 @@
         <v>1</v>
       </c>
       <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -11497,7 +11495,9 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>1</v>
@@ -11507,26 +11507,26 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -11541,35 +11541,35 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -11602,13 +11602,13 @@
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
@@ -11618,9 +11618,7 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -11629,17 +11627,19 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
@@ -11664,7 +11664,9 @@
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -11673,26 +11675,24 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
         <v>1</v>
@@ -11709,7 +11709,9 @@
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -11719,25 +11721,25 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
@@ -11747,9 +11749,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -11764,12 +11764,12 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -11777,9 +11777,7 @@
       <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="n">
         <v>1</v>
@@ -11788,26 +11786,30 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -11815,14 +11817,14 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -11841,9 +11843,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11884,10 +11884,10 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -11897,20 +11897,22 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
@@ -11923,9 +11925,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -11936,7 +11936,9 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -11954,24 +11956,22 @@
         <v>1</v>
       </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -11992,32 +11992,32 @@
       <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -12028,9 +12028,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -12049,7 +12047,9 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
@@ -12070,7 +12070,9 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -12082,45 +12084,41 @@
         <v>1</v>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -12134,10 +12132,10 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
         <v>1</v>
@@ -12150,7 +12148,9 @@
         <v>1</v>
       </c>
       <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
@@ -12160,23 +12160,23 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -12189,11 +12189,11 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>

--- a/Data/04_26_schedule_results.xlsx
+++ b/Data/04_26_schedule_results.xlsx
@@ -538,11 +538,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -558,7 +558,7 @@
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>500</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3">
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -614,7 +614,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4">
@@ -650,18 +650,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>3.5</v>
@@ -670,7 +670,7 @@
         <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>610</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5">
@@ -706,11 +706,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -726,7 +726,7 @@
         <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>630</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6">
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>3.5</v>
@@ -874,18 +874,18 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>3.5</v>
@@ -894,7 +894,7 @@
         <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9">
@@ -930,18 +930,18 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>3.5</v>
@@ -950,7 +950,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>400</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10">
@@ -986,18 +986,18 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>3.5</v>
@@ -1006,7 +1006,7 @@
         <v>70</v>
       </c>
       <c r="N10" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1062,7 +1062,7 @@
         <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12">
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1230,7 +1230,7 @@
         <v>70</v>
       </c>
       <c r="N14" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15">
@@ -1277,7 +1277,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
         <v>3.5</v>
@@ -1378,11 +1378,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Ömmi</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1398,7 +1398,7 @@
         <v>80</v>
       </c>
       <c r="N17" t="n">
-        <v>620</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18">
@@ -1434,18 +1434,18 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1454,7 +1454,7 @@
         <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>470</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19">
@@ -1490,18 +1490,18 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1510,7 +1510,7 @@
         <v>70</v>
       </c>
       <c r="N19" t="n">
-        <v>570</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20">
@@ -1546,18 +1546,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1566,7 +1566,7 @@
         <v>70</v>
       </c>
       <c r="N20" t="n">
-        <v>530</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21">
@@ -1602,18 +1602,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1622,7 +1622,7 @@
         <v>70</v>
       </c>
       <c r="N21" t="n">
-        <v>610</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22">
@@ -1658,18 +1658,18 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1678,7 +1678,7 @@
         <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23">
@@ -1714,18 +1714,18 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1734,7 +1734,7 @@
         <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>480</v>
+        <v>690</v>
       </c>
     </row>
     <row r="24">
@@ -1837,7 +1837,7 @@
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1893,7 +1893,7 @@
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1938,18 +1938,18 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
         <v>3</v>
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="N27" t="n">
-        <v>560</v>
+        <v>613.3</v>
       </c>
     </row>
     <row r="28">
@@ -2005,7 +2005,7 @@
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -2218,18 +2218,18 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2238,7 +2238,7 @@
         <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>540</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33">
@@ -2274,18 +2274,18 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2294,7 +2294,7 @@
         <v>70</v>
       </c>
       <c r="N33" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34">
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>4</v>
@@ -2498,15 +2498,15 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>90</v>
       </c>
       <c r="N37" t="n">
-        <v>503.3</v>
+        <v>510</v>
       </c>
     </row>
     <row r="38">
@@ -2554,11 +2554,11 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2574,7 +2574,7 @@
         <v>50</v>
       </c>
       <c r="N38" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="39">
@@ -2610,18 +2610,18 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J39" t="n">
         <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>3.5</v>
@@ -2630,7 +2630,7 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>420</v>
+        <v>530</v>
       </c>
     </row>
     <row r="40">
@@ -2666,18 +2666,18 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J40" t="n">
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>3.5</v>
@@ -2686,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>530</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41">
@@ -2722,18 +2722,18 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L41" t="n">
         <v>3.5</v>
@@ -2742,7 +2742,7 @@
         <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
     </row>
     <row r="42">
@@ -2778,18 +2778,18 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J42" t="n">
         <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L42" t="n">
         <v>3.5</v>
@@ -2798,7 +2798,7 @@
         <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>660</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43">
@@ -2834,18 +2834,18 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L43" t="n">
         <v>3.5</v>
@@ -2854,7 +2854,7 @@
         <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="44">
@@ -2890,18 +2890,18 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L44" t="n">
         <v>3.5</v>
@@ -2910,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>530</v>
+        <v>630</v>
       </c>
     </row>
     <row r="45">
@@ -2946,18 +2946,18 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
         <v>3.5</v>
@@ -2966,7 +2966,7 @@
         <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
     </row>
     <row r="46">
@@ -3002,18 +3002,18 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L46" t="n">
         <v>3.5</v>
@@ -3022,7 +3022,7 @@
         <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>610</v>
+        <v>700</v>
       </c>
     </row>
     <row r="47">
@@ -3058,18 +3058,18 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J47" t="n">
         <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L47" t="n">
         <v>3.5</v>
@@ -3078,7 +3078,7 @@
         <v>50</v>
       </c>
       <c r="N47" t="n">
-        <v>680</v>
+        <v>663.3</v>
       </c>
     </row>
     <row r="48">
@@ -3181,7 +3181,7 @@
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>3.5</v>
@@ -3190,7 +3190,7 @@
         <v>50</v>
       </c>
       <c r="N49" t="n">
-        <v>660</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50">
@@ -3237,7 +3237,7 @@
         <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
         <v>3.5</v>
@@ -3246,7 +3246,7 @@
         <v>50</v>
       </c>
       <c r="N50" t="n">
-        <v>720</v>
+        <v>670</v>
       </c>
     </row>
     <row r="51">
@@ -3282,18 +3282,18 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
         <v>3.5</v>
@@ -3302,7 +3302,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>463.3</v>
+        <v>713.3</v>
       </c>
     </row>
     <row r="52">
@@ -3338,18 +3338,18 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>3.5</v>
@@ -3358,7 +3358,7 @@
         <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>670</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="53">
@@ -3405,7 +3405,7 @@
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
         <v>3.5</v>
@@ -3414,7 +3414,7 @@
         <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>710</v>
+        <v>680</v>
       </c>
     </row>
     <row r="54">
@@ -3461,7 +3461,7 @@
         <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L54" t="n">
         <v>3.5</v>
@@ -3517,7 +3517,7 @@
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L55" t="n">
         <v>3.5</v>
@@ -3526,7 +3526,7 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56">
@@ -3573,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3618,18 +3618,18 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L57" t="n">
         <v>3.5</v>
@@ -3638,7 +3638,7 @@
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>480</v>
+        <v>713.3</v>
       </c>
     </row>
     <row r="58">
@@ -3730,11 +3730,11 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3750,7 +3750,7 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>630</v>
+        <v>580</v>
       </c>
     </row>
     <row r="60">
@@ -3806,7 +3806,7 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>480</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61">
@@ -3842,18 +3842,18 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L61" t="n">
         <v>4</v>
@@ -3862,7 +3862,7 @@
         <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>540</v>
+        <v>750</v>
       </c>
     </row>
     <row r="62">
@@ -3898,18 +3898,18 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J62" t="n">
         <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L62" t="n">
         <v>4</v>
@@ -3918,7 +3918,7 @@
         <v>50</v>
       </c>
       <c r="N62" t="n">
-        <v>730</v>
+        <v>750</v>
       </c>
     </row>
     <row r="63">
@@ -3954,18 +3954,18 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -3974,7 +3974,7 @@
         <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>780</v>
+        <v>510</v>
       </c>
     </row>
     <row r="64">
@@ -4010,18 +4010,18 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -4030,7 +4030,7 @@
         <v>50</v>
       </c>
       <c r="N64" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
     </row>
     <row r="65">
@@ -4066,18 +4066,18 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>4</v>
@@ -4086,7 +4086,7 @@
         <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>750</v>
+        <v>480</v>
       </c>
     </row>
     <row r="66">
@@ -4122,18 +4122,18 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L66" t="n">
         <v>4</v>
@@ -4142,7 +4142,7 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="67">
@@ -4189,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -4198,7 +4198,7 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="68">
@@ -4245,7 +4245,7 @@
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -4254,7 +4254,7 @@
         <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>730</v>
+        <v>800</v>
       </c>
     </row>
     <row r="69">
@@ -4301,7 +4301,7 @@
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -4310,7 +4310,7 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="70">
@@ -4346,11 +4346,11 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Róbert </t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4366,7 +4366,7 @@
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>580</v>
+        <v>610</v>
       </c>
     </row>
     <row r="71">
@@ -4422,7 +4422,7 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
     </row>
     <row r="72">
@@ -4458,11 +4458,11 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4514,11 +4514,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4534,7 +4534,7 @@
         <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>490</v>
+        <v>420</v>
       </c>
     </row>
     <row r="74">
@@ -4570,11 +4570,11 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4590,7 +4590,7 @@
         <v>40</v>
       </c>
       <c r="N74" t="n">
-        <v>560</v>
+        <v>490</v>
       </c>
     </row>
     <row r="75">
@@ -4646,7 +4646,7 @@
         <v>80</v>
       </c>
       <c r="N75" t="n">
-        <v>573.3</v>
+        <v>543.3</v>
       </c>
     </row>
     <row r="76">
@@ -4738,11 +4738,11 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4758,7 +4758,7 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
     </row>
     <row r="78">
@@ -4794,11 +4794,11 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4814,7 +4814,7 @@
         <v>80</v>
       </c>
       <c r="N78" t="n">
-        <v>490</v>
+        <v>543.3</v>
       </c>
     </row>
     <row r="79">
@@ -4906,18 +4906,18 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J80" t="n">
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L80" t="n">
         <v>3</v>
@@ -4926,7 +4926,7 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>693.3</v>
+        <v>673.3</v>
       </c>
     </row>
     <row r="81">
@@ -4973,7 +4973,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L81" t="n">
         <v>3</v>
@@ -4982,7 +4982,7 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>680</v>
+        <v>750</v>
       </c>
     </row>
     <row r="82">
@@ -5018,18 +5018,18 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -5038,7 +5038,7 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>730</v>
+        <v>470</v>
       </c>
     </row>
     <row r="83">
@@ -5074,11 +5074,11 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -5094,7 +5094,7 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="84">
@@ -5130,18 +5130,18 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J84" t="n">
         <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L84" t="n">
         <v>3</v>
@@ -5150,7 +5150,7 @@
         <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>740</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85">
@@ -5186,18 +5186,18 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Rut </t>
         </is>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -5206,7 +5206,7 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>690</v>
+        <v>740</v>
       </c>
     </row>
     <row r="86">
@@ -5253,7 +5253,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L86" t="n">
         <v>3</v>
@@ -5262,7 +5262,7 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="87">
@@ -5298,18 +5298,18 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
         <v>3</v>
@@ -5318,7 +5318,7 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>553.3</v>
+        <v>470</v>
       </c>
     </row>
     <row r="88">
@@ -5365,7 +5365,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5374,7 +5374,7 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="89">
@@ -5421,7 +5421,7 @@
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -5430,7 +5430,7 @@
         <v>50</v>
       </c>
       <c r="N89" t="n">
-        <v>730</v>
+        <v>750</v>
       </c>
     </row>
     <row r="90">
@@ -5542,7 +5542,7 @@
         <v>70</v>
       </c>
       <c r="N91" t="n">
-        <v>643.3</v>
+        <v>613.3</v>
       </c>
     </row>
     <row r="92">
@@ -5578,11 +5578,11 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5634,11 +5634,11 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5869,7 +5869,7 @@
         <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L97" t="n">
         <v>5.5</v>
@@ -5878,7 +5878,7 @@
         <v>70</v>
       </c>
       <c r="N97" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="98">
@@ -5925,7 +5925,7 @@
         <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
         <v>5.5</v>
@@ -5934,7 +5934,7 @@
         <v>70</v>
       </c>
       <c r="N98" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99">
@@ -6082,18 +6082,18 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J101" t="n">
         <v>2</v>
       </c>
       <c r="K101" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L101" t="n">
         <v>5.5</v>
@@ -6102,7 +6102,7 @@
         <v>70</v>
       </c>
       <c r="N101" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102">
@@ -6138,18 +6138,18 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L102" t="n">
         <v>5.5</v>
@@ -6158,7 +6158,7 @@
         <v>70</v>
       </c>
       <c r="N102" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="103">
@@ -6194,18 +6194,18 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L103" t="n">
         <v>5.5</v>
@@ -6214,7 +6214,7 @@
         <v>70</v>
       </c>
       <c r="N103" t="n">
-        <v>410</v>
+        <v>590</v>
       </c>
     </row>
     <row r="104">
@@ -6250,18 +6250,18 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J104" t="n">
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L104" t="n">
         <v>5.5</v>
@@ -6270,7 +6270,7 @@
         <v>70</v>
       </c>
       <c r="N104" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="105">
@@ -6317,7 +6317,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L105" t="n">
         <v>5.5</v>
@@ -6438,7 +6438,7 @@
         <v>70</v>
       </c>
       <c r="N107" t="n">
-        <v>430</v>
+        <v>480</v>
       </c>
     </row>
     <row r="108">
@@ -6485,7 +6485,7 @@
         <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L108" t="n">
         <v>4</v>
@@ -6530,18 +6530,18 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J109" t="n">
         <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L109" t="n">
         <v>4</v>
@@ -6550,7 +6550,7 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>693.3</v>
+        <v>660</v>
       </c>
     </row>
     <row r="110">
@@ -6586,18 +6586,18 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J110" t="n">
         <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L110" t="n">
         <v>4</v>
@@ -6606,7 +6606,7 @@
         <v>70</v>
       </c>
       <c r="N110" t="n">
-        <v>570</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111">
@@ -6642,18 +6642,18 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L111" t="n">
         <v>4</v>
@@ -6662,7 +6662,7 @@
         <v>70</v>
       </c>
       <c r="N111" t="n">
-        <v>400</v>
+        <v>570</v>
       </c>
     </row>
     <row r="112">
@@ -6698,18 +6698,18 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J112" t="n">
         <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
         <v>4</v>
@@ -6718,7 +6718,7 @@
         <v>70</v>
       </c>
       <c r="N112" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
     </row>
     <row r="113">
@@ -6754,18 +6754,18 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Sara Júlía </t>
         </is>
       </c>
       <c r="J113" t="n">
         <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L113" t="n">
         <v>4</v>
@@ -6774,7 +6774,7 @@
         <v>70</v>
       </c>
       <c r="N113" t="n">
-        <v>350</v>
+        <v>430</v>
       </c>
     </row>
     <row r="114">
@@ -6810,18 +6810,18 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J114" t="n">
         <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L114" t="n">
         <v>4</v>
@@ -6830,7 +6830,7 @@
         <v>70</v>
       </c>
       <c r="N114" t="n">
-        <v>753.3</v>
+        <v>350</v>
       </c>
     </row>
     <row r="115">
@@ -6877,7 +6877,7 @@
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L115" t="n">
         <v>4</v>
@@ -6886,7 +6886,7 @@
         <v>70</v>
       </c>
       <c r="N115" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="116">
@@ -6978,18 +6978,18 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Róbert </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J117" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L117" t="n">
         <v>4</v>
@@ -6998,7 +6998,7 @@
         <v>70</v>
       </c>
       <c r="N117" t="n">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="118">
@@ -7034,11 +7034,11 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -7054,7 +7054,7 @@
         <v>70</v>
       </c>
       <c r="N118" t="n">
-        <v>470</v>
+        <v>650</v>
       </c>
     </row>
     <row r="119">
@@ -7090,18 +7090,18 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J119" t="n">
         <v>2</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
         <v>4</v>
@@ -7110,7 +7110,7 @@
         <v>80</v>
       </c>
       <c r="N119" t="n">
-        <v>620</v>
+        <v>570</v>
       </c>
     </row>
     <row r="120">
@@ -7157,7 +7157,7 @@
         <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
         <v>4</v>
@@ -7166,7 +7166,7 @@
         <v>80</v>
       </c>
       <c r="N120" t="n">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="121">
@@ -7202,11 +7202,11 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t xml:space="preserve">Erna </t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -7222,7 +7222,7 @@
         <v>80</v>
       </c>
       <c r="N121" t="n">
-        <v>570</v>
+        <v>650</v>
       </c>
     </row>
     <row r="122">
@@ -7314,15 +7314,15 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -7334,7 +7334,7 @@
         <v>90</v>
       </c>
       <c r="N123" t="n">
-        <v>510</v>
+        <v>530</v>
       </c>
     </row>
     <row r="124">
@@ -7370,18 +7370,18 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J124" t="n">
         <v>2</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
@@ -7390,7 +7390,7 @@
         <v>80</v>
       </c>
       <c r="N124" t="n">
-        <v>620</v>
+        <v>623.3</v>
       </c>
     </row>
     <row r="125">
@@ -7426,18 +7426,18 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J125" t="n">
         <v>2</v>
       </c>
       <c r="K125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
         <v>3</v>
@@ -7446,7 +7446,7 @@
         <v>80</v>
       </c>
       <c r="N125" t="n">
-        <v>623.3</v>
+        <v>580</v>
       </c>
     </row>
     <row r="126">
@@ -7482,18 +7482,18 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Sara B</t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J126" t="n">
         <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L126" t="n">
         <v>3</v>
@@ -7502,7 +7502,7 @@
         <v>80</v>
       </c>
       <c r="N126" t="n">
-        <v>530</v>
+        <v>650</v>
       </c>
     </row>
     <row r="127">
@@ -7538,18 +7538,18 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J127" t="n">
         <v>2</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7558,7 +7558,7 @@
         <v>80</v>
       </c>
       <c r="N127" t="n">
-        <v>633.3</v>
+        <v>700</v>
       </c>
     </row>
     <row r="128">
@@ -7594,18 +7594,18 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L128" t="n">
         <v>3</v>
@@ -7614,7 +7614,7 @@
         <v>50</v>
       </c>
       <c r="N128" t="n">
-        <v>590</v>
+        <v>670</v>
       </c>
     </row>
     <row r="129">
@@ -7650,18 +7650,18 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hólmfríður </t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J129" t="n">
         <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L129" t="n">
         <v>3</v>
@@ -7670,7 +7670,7 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>460</v>
+        <v>590</v>
       </c>
     </row>
     <row r="130">
@@ -7706,18 +7706,18 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Katrín Hel</t>
+          <t xml:space="preserve">Hólmfríður </t>
         </is>
       </c>
       <c r="J130" t="n">
         <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7726,7 +7726,7 @@
         <v>50</v>
       </c>
       <c r="N130" t="n">
-        <v>393.3</v>
+        <v>460</v>
       </c>
     </row>
     <row r="131">
@@ -7762,18 +7762,18 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Katrín Hel</t>
         </is>
       </c>
       <c r="J131" t="n">
         <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
         <v>3</v>
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="N131" t="n">
-        <v>410</v>
+        <v>393.3</v>
       </c>
     </row>
     <row r="132">
@@ -7818,18 +7818,18 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigríður </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>2</v>
       </c>
       <c r="K132" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L132" t="n">
         <v>3</v>
@@ -7838,7 +7838,7 @@
         <v>50</v>
       </c>
       <c r="N132" t="n">
-        <v>740</v>
+        <v>410</v>
       </c>
     </row>
     <row r="133">
@@ -7885,7 +7885,7 @@
         <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7894,7 +7894,7 @@
         <v>50</v>
       </c>
       <c r="N133" t="n">
-        <v>610</v>
+        <v>660</v>
       </c>
     </row>
     <row r="134">
@@ -7941,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="K134" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
         <v>3</v>
@@ -7950,7 +7950,7 @@
         <v>50</v>
       </c>
       <c r="N134" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
     </row>
     <row r="135">
@@ -7986,18 +7986,18 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elísabet </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J135" t="n">
         <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
         <v>4</v>
@@ -8006,7 +8006,7 @@
         <v>80</v>
       </c>
       <c r="N135" t="n">
-        <v>493.3</v>
+        <v>370</v>
       </c>
     </row>
     <row r="136">
@@ -8042,18 +8042,18 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guðný  </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J136" t="n">
         <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="n">
         <v>4</v>
@@ -8062,7 +8062,7 @@
         <v>80</v>
       </c>
       <c r="N136" t="n">
-        <v>370</v>
+        <v>550</v>
       </c>
     </row>
     <row r="137">
@@ -8154,11 +8154,11 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -8210,11 +8210,11 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -8230,7 +8230,7 @@
         <v>80</v>
       </c>
       <c r="N139" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="140">
@@ -8266,18 +8266,18 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erna </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J140" t="n">
         <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L140" t="n">
         <v>4</v>
@@ -8286,7 +8286,7 @@
         <v>50</v>
       </c>
       <c r="N140" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
     </row>
     <row r="141">
@@ -8322,18 +8322,18 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaukur </t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J141" t="n">
         <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L141" t="n">
         <v>4</v>
@@ -8342,7 +8342,7 @@
         <v>50</v>
       </c>
       <c r="N141" t="n">
-        <v>470</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="142">
@@ -8378,18 +8378,18 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Gréta</t>
+          <t xml:space="preserve">Gaukur </t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L142" t="n">
         <v>4</v>
@@ -8398,7 +8398,7 @@
         <v>50</v>
       </c>
       <c r="N142" t="n">
-        <v>630</v>
+        <v>470</v>
       </c>
     </row>
     <row r="143">
@@ -8434,11 +8434,11 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -8490,18 +8490,18 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J144" t="n">
         <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L144" t="n">
         <v>4</v>
@@ -8510,7 +8510,7 @@
         <v>50</v>
       </c>
       <c r="N144" t="n">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="145">
@@ -8546,18 +8546,18 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Jórunn  </t>
         </is>
       </c>
       <c r="J145" t="n">
         <v>2</v>
       </c>
       <c r="K145" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L145" t="n">
         <v>4</v>
@@ -8566,7 +8566,7 @@
         <v>50</v>
       </c>
       <c r="N145" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146">
@@ -8602,18 +8602,18 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J146" t="n">
         <v>2</v>
       </c>
       <c r="K146" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L146" t="n">
         <v>4</v>
@@ -8622,7 +8622,7 @@
         <v>50</v>
       </c>
       <c r="N146" t="n">
-        <v>580</v>
+        <v>470</v>
       </c>
     </row>
     <row r="147">
@@ -8658,11 +8658,11 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Sveinn</t>
+          <t xml:space="preserve">Magnús  </t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -8678,7 +8678,7 @@
         <v>50</v>
       </c>
       <c r="N147" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row r="148">
@@ -8714,18 +8714,18 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdís </t>
+          <t xml:space="preserve">Sigríður </t>
         </is>
       </c>
       <c r="J148" t="n">
         <v>2</v>
       </c>
       <c r="K148" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L148" t="n">
         <v>4</v>
@@ -8734,7 +8734,7 @@
         <v>50</v>
       </c>
       <c r="N148" t="n">
-        <v>410</v>
+        <v>570</v>
       </c>
     </row>
     <row r="149">
@@ -8770,18 +8770,18 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védís </t>
+          <t>Sveinn</t>
         </is>
       </c>
       <c r="J149" t="n">
         <v>2</v>
       </c>
       <c r="K149" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L149" t="n">
         <v>4</v>
@@ -8790,7 +8790,7 @@
         <v>50</v>
       </c>
       <c r="N149" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
     </row>
     <row r="150">
@@ -8826,18 +8826,18 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Sæmundur </t>
         </is>
       </c>
       <c r="J150" t="n">
         <v>2</v>
       </c>
       <c r="K150" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L150" t="n">
         <v>4</v>
@@ -8846,7 +8846,7 @@
         <v>50</v>
       </c>
       <c r="N150" t="n">
-        <v>610</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="151">
@@ -9162,18 +9162,18 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrín Sig </t>
+          <t>Orri</t>
         </is>
       </c>
       <c r="J156" t="n">
         <v>2</v>
       </c>
       <c r="K156" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L156" t="n">
         <v>4</v>
@@ -9182,7 +9182,7 @@
         <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>690</v>
+        <v>360</v>
       </c>
     </row>
     <row r="157">
@@ -9218,18 +9218,18 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Orri</t>
+          <t>Sara B</t>
         </is>
       </c>
       <c r="J157" t="n">
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L157" t="n">
         <v>4</v>
@@ -9238,7 +9238,7 @@
         <v>70</v>
       </c>
       <c r="N157" t="n">
-        <v>360</v>
+        <v>520</v>
       </c>
     </row>
     <row r="158">
@@ -9274,18 +9274,18 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara Júlía </t>
+          <t xml:space="preserve">Jara </t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>4</v>
@@ -9294,7 +9294,7 @@
         <v>70</v>
       </c>
       <c r="N158" t="n">
-        <v>620</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159">
@@ -9330,18 +9330,18 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jara </t>
+          <t xml:space="preserve">Þórey </t>
         </is>
       </c>
       <c r="J159" t="n">
         <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L159" t="n">
         <v>4</v>
@@ -9350,7 +9350,7 @@
         <v>70</v>
       </c>
       <c r="N159" t="n">
-        <v>400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="160">
@@ -9386,18 +9386,18 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jórunn  </t>
+          <t xml:space="preserve">Katrín Sig </t>
         </is>
       </c>
       <c r="J160" t="n">
         <v>2</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
@@ -9406,7 +9406,7 @@
         <v>80</v>
       </c>
       <c r="N160" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="161">
@@ -9442,18 +9442,18 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnús  </t>
+          <t xml:space="preserve">Unnar </t>
         </is>
       </c>
       <c r="J161" t="n">
         <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" t="n">
         <v>3</v>
@@ -9462,7 +9462,7 @@
         <v>80</v>
       </c>
       <c r="N161" t="n">
-        <v>530</v>
+        <v>630</v>
       </c>
     </row>
     <row r="162">
@@ -9498,11 +9498,11 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnar </t>
+          <t xml:space="preserve">Védís </t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -9518,7 +9518,7 @@
         <v>90</v>
       </c>
       <c r="N162" t="n">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="163">
@@ -9565,7 +9565,7 @@
         <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -9574,7 +9574,7 @@
         <v>50</v>
       </c>
       <c r="N163" t="n">
-        <v>530</v>
+        <v>580</v>
       </c>
     </row>
     <row r="164">
@@ -9610,18 +9610,18 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Soffía </t>
+          <t>Arnar Ragn</t>
         </is>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L164" t="n">
         <v>3</v>
@@ -9630,7 +9630,7 @@
         <v>50</v>
       </c>
       <c r="N164" t="n">
-        <v>460</v>
+        <v>620</v>
       </c>
     </row>
     <row r="165">
@@ -9666,18 +9666,18 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Arnar Ragn</t>
+          <t xml:space="preserve">Elísabet </t>
         </is>
       </c>
       <c r="J165" t="n">
         <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>
@@ -9686,7 +9686,7 @@
         <v>50</v>
       </c>
       <c r="N165" t="n">
-        <v>670</v>
+        <v>663.3</v>
       </c>
     </row>
     <row r="166">
@@ -9722,11 +9722,11 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Hrafnkell</t>
+          <t>Gréta</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -9778,18 +9778,18 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hrannar </t>
+          <t xml:space="preserve">Guðný  </t>
         </is>
       </c>
       <c r="J167" t="n">
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L167" t="n">
         <v>3</v>
@@ -9798,7 +9798,7 @@
         <v>50</v>
       </c>
       <c r="N167" t="n">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row r="168">
@@ -9834,18 +9834,18 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laufey </t>
+          <t>Hrafnkell</t>
         </is>
       </c>
       <c r="J168" t="n">
         <v>2</v>
       </c>
       <c r="K168" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L168" t="n">
         <v>3</v>
@@ -9854,7 +9854,7 @@
         <v>50</v>
       </c>
       <c r="N168" t="n">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="169">
@@ -9890,18 +9890,18 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rut </t>
+          <t xml:space="preserve">Hrannar </t>
         </is>
       </c>
       <c r="J169" t="n">
         <v>2</v>
       </c>
       <c r="K169" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
@@ -9910,7 +9910,7 @@
         <v>50</v>
       </c>
       <c r="N169" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="170">
@@ -9946,18 +9946,18 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma </t>
+          <t xml:space="preserve">Laufey </t>
         </is>
       </c>
       <c r="J170" t="n">
         <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L170" t="n">
         <v>3</v>
@@ -9966,7 +9966,7 @@
         <v>50</v>
       </c>
       <c r="N170" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="171">
@@ -10002,18 +10002,18 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sæmundur </t>
+          <t xml:space="preserve">Selma </t>
         </is>
       </c>
       <c r="J171" t="n">
         <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L171" t="n">
         <v>3</v>
@@ -10022,7 +10022,7 @@
         <v>50</v>
       </c>
       <c r="N171" t="n">
-        <v>683.3</v>
+        <v>400</v>
       </c>
     </row>
     <row r="172">
@@ -10058,18 +10058,18 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnar </t>
+          <t xml:space="preserve">Valdís </t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
@@ -10078,7 +10078,7 @@
         <v>50</v>
       </c>
       <c r="N172" t="n">
-        <v>530</v>
+        <v>600</v>
       </c>
     </row>
     <row r="173">
@@ -10114,18 +10114,18 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Þórey </t>
+          <t xml:space="preserve">Arnar </t>
         </is>
       </c>
       <c r="J173" t="n">
         <v>1</v>
       </c>
       <c r="K173" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
         <v>3</v>
@@ -10134,7 +10134,7 @@
         <v>50</v>
       </c>
       <c r="N173" t="n">
-        <v>680</v>
+        <v>530</v>
       </c>
     </row>
     <row r="174">
@@ -10170,11 +10170,11 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmar </t>
+          <t xml:space="preserve">Anna Soffía </t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -10190,7 +10190,7 @@
         <v>80</v>
       </c>
       <c r="N174" t="n">
-        <v>543.3</v>
+        <v>550</v>
       </c>
     </row>
     <row r="175">
@@ -10226,11 +10226,11 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Ömmi</t>
+          <t xml:space="preserve">Elmar </t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -10246,7 +10246,7 @@
         <v>80</v>
       </c>
       <c r="N175" t="n">
-        <v>510</v>
+        <v>543.3</v>
       </c>
     </row>
   </sheetData>
@@ -10502,10 +10502,10 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -10531,10 +10531,10 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -10561,27 +10561,27 @@
       <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -10718,7 +10718,9 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1</v>
@@ -10726,9 +10728,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>1</v>
       </c>
@@ -10746,7 +10746,9 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10769,14 +10771,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -10800,23 +10802,21 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -10828,12 +10828,12 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -10892,9 +10892,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -10910,10 +10908,10 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -10928,7 +10926,9 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10937,9 +10937,7 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -10949,9 +10947,7 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -10962,7 +10958,9 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -10975,7 +10973,9 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11000,10 +11000,10 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -11126,18 +11126,20 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -11152,9 +11154,7 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -11200,7 +11200,9 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
@@ -11210,7 +11212,9 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>1</v>
@@ -11219,12 +11223,8 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -11232,13 +11232,15 @@
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -11328,9 +11330,7 @@
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -11348,7 +11348,9 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -11356,16 +11358,16 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -11488,16 +11490,16 @@
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>1</v>
@@ -11506,7 +11508,9 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
@@ -11517,16 +11521,12 @@
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -11561,11 +11561,11 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
@@ -11586,17 +11586,19 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
@@ -11606,9 +11608,7 @@
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
@@ -11626,11 +11626,11 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -11661,9 +11661,7 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>1</v>
       </c>
@@ -11673,7 +11671,9 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>1</v>
@@ -11681,23 +11681,23 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
@@ -11708,7 +11708,9 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
@@ -11718,9 +11720,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>1</v>
@@ -11734,12 +11734,12 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
@@ -11758,45 +11758,45 @@
       <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -11805,27 +11805,25 @@
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
@@ -11843,7 +11841,9 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11894,9 +11894,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>1</v>
@@ -11917,14 +11915,16 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -11981,7 +11981,9 @@
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -12015,9 +12017,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -12034,10 +12034,10 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -12084,7 +12084,9 @@
         <v>1</v>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -12094,9 +12096,7 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
@@ -12169,11 +12169,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>1</v>
       </c>
@@ -12186,22 +12186,22 @@
       <c r="S42" t="n">
         <v>1</v>
       </c>
-      <c r="T42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="n">
-        <v>1</v>
-      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
